--- a/sample-data/LD_enrollments_2026-05.xlsx
+++ b/sample-data/LD_enrollments_2026-05.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H185"/>
+  <dimension ref="A1:H169"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -430,516 +430,516 @@
         <v>AP0001</v>
       </c>
       <c r="B2" t="str">
-        <v>LDP-009</v>
+        <v>LDP-004</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-03-12</v>
+        <v>2026-03-18</v>
       </c>
       <c r="D2" t="str">
-        <v>Completed</v>
+        <v>In-progress</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-04-08</v>
+        <v/>
       </c>
       <c r="F2">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>58</v>
-      </c>
-      <c r="H2">
-        <v>4.9</v>
+        <v>10</v>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>AP0001</v>
+        <v>AP0002</v>
       </c>
       <c r="B3" t="str">
-        <v>LDP-010</v>
+        <v>LDP-002</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-21</v>
       </c>
       <c r="D3" t="str">
         <v>Completed</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-05-19</v>
+        <v>2026-04-27</v>
       </c>
       <c r="F3">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="H3">
-        <v>4.3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>AP0001</v>
+        <v>AP0002</v>
       </c>
       <c r="B4" t="str">
-        <v>LDP-004</v>
+        <v>LDP-010</v>
       </c>
       <c r="C4" t="str">
-        <v>2026-03-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="D4" t="str">
-        <v>Dropped</v>
+        <v>Completed</v>
       </c>
       <c r="E4" t="str">
-        <v/>
+        <v>2026-04-12</v>
       </c>
       <c r="F4">
-        <v>7</v>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
+        <v>13</v>
+      </c>
+      <c r="G4">
+        <v>56</v>
+      </c>
+      <c r="H4">
+        <v>3.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>AP0002</v>
+        <v>AP0003</v>
       </c>
       <c r="B5" t="str">
-        <v>LDP-001</v>
+        <v>LDP-010</v>
       </c>
       <c r="C5" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-21</v>
       </c>
       <c r="D5" t="str">
         <v>Completed</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-07</v>
       </c>
       <c r="F5">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="H5">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>AP0002</v>
+        <v>AP0005</v>
       </c>
       <c r="B6" t="str">
-        <v>LDP-007</v>
+        <v>LDP-002</v>
       </c>
       <c r="C6" t="str">
-        <v>2026-05-01</v>
+        <v>2026-03-18</v>
       </c>
       <c r="D6" t="str">
-        <v>Enrolled</v>
+        <v>Completed</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>2026-04-14</v>
       </c>
       <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>79</v>
+      </c>
+      <c r="H6">
+        <v>4.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>AP0004</v>
+        <v>AP0005</v>
       </c>
       <c r="B7" t="str">
-        <v>LDP-003</v>
+        <v>LDP-010</v>
       </c>
       <c r="C7" t="str">
-        <v>2026-03-08</v>
+        <v>2026-05-25</v>
       </c>
       <c r="D7" t="str">
         <v>Completed</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-07</v>
       </c>
       <c r="F7">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G7">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>AP0004</v>
+        <v>AP0006</v>
       </c>
       <c r="B8" t="str">
-        <v>LDP-005</v>
+        <v>LDP-007</v>
       </c>
       <c r="C8" t="str">
-        <v>2026-03-02</v>
+        <v>2026-04-07</v>
       </c>
       <c r="D8" t="str">
-        <v>Enrolled</v>
+        <v>Completed</v>
       </c>
       <c r="E8" t="str">
-        <v/>
+        <v>2026-04-25</v>
       </c>
       <c r="F8">
-        <v>5</v>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
+        <v>12</v>
+      </c>
+      <c r="G8">
+        <v>65</v>
+      </c>
+      <c r="H8">
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>AP0005</v>
+        <v>AP0007</v>
       </c>
       <c r="B9" t="str">
         <v>LDP-003</v>
       </c>
       <c r="C9" t="str">
-        <v>2026-03-18</v>
+        <v>2026-05-03</v>
       </c>
       <c r="D9" t="str">
-        <v>Enrolled</v>
+        <v>Completed</v>
       </c>
       <c r="E9" t="str">
-        <v/>
+        <v>2026-04-06</v>
       </c>
       <c r="F9">
-        <v>2</v>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
+        <v>13</v>
+      </c>
+      <c r="G9">
+        <v>76</v>
+      </c>
+      <c r="H9">
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>AP0005</v>
+        <v>AP0009</v>
       </c>
       <c r="B10" t="str">
-        <v>LDP-005</v>
+        <v>LDP-009</v>
       </c>
       <c r="C10" t="str">
-        <v>2026-05-14</v>
+        <v>2026-04-18</v>
       </c>
       <c r="D10" t="str">
         <v>Completed</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-06</v>
       </c>
       <c r="F10">
         <v>12</v>
       </c>
       <c r="G10">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="H10">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>AP0005</v>
+        <v>AP0009</v>
       </c>
       <c r="B11" t="str">
-        <v>LDP-002</v>
+        <v>LDP-008</v>
       </c>
       <c r="C11" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="D11" t="str">
         <v>Completed</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-20</v>
       </c>
       <c r="F11">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G11">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H11">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>AP0006</v>
+        <v>AP0009</v>
       </c>
       <c r="B12" t="str">
-        <v>LDP-005</v>
+        <v>LDP-002</v>
       </c>
       <c r="C12" t="str">
-        <v>2026-03-13</v>
+        <v>2026-05-12</v>
       </c>
       <c r="D12" t="str">
-        <v>Dropped</v>
+        <v>Completed</v>
       </c>
       <c r="E12" t="str">
-        <v/>
+        <v>2026-05-05</v>
       </c>
       <c r="F12">
-        <v>3</v>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
+        <v>13</v>
+      </c>
+      <c r="G12">
+        <v>78</v>
+      </c>
+      <c r="H12">
+        <v>4.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>AP0007</v>
+        <v>AP0010</v>
       </c>
       <c r="B13" t="str">
-        <v>LDP-002</v>
+        <v>LDP-004</v>
       </c>
       <c r="C13" t="str">
-        <v>2026-04-05</v>
+        <v>2026-05-14</v>
       </c>
       <c r="D13" t="str">
-        <v>Enrolled</v>
+        <v>Completed</v>
       </c>
       <c r="E13" t="str">
-        <v/>
+        <v>2026-05-25</v>
       </c>
       <c r="F13">
-        <v>13</v>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
+        <v>16</v>
+      </c>
+      <c r="G13">
+        <v>96</v>
+      </c>
+      <c r="H13">
+        <v>4.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>AP0008</v>
+        <v>AP0010</v>
       </c>
       <c r="B14" t="str">
-        <v>LDP-010</v>
+        <v>LDP-003</v>
       </c>
       <c r="C14" t="str">
-        <v>2026-05-04</v>
+        <v>2026-04-11</v>
       </c>
       <c r="D14" t="str">
-        <v>Dropped</v>
+        <v>Completed</v>
       </c>
       <c r="E14" t="str">
-        <v/>
+        <v>2026-04-11</v>
       </c>
       <c r="F14">
-        <v>3</v>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v/>
+        <v>5</v>
+      </c>
+      <c r="G14">
+        <v>82</v>
+      </c>
+      <c r="H14">
+        <v>3.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>AP0008</v>
+        <v>AP0013</v>
       </c>
       <c r="B15" t="str">
         <v>LDP-004</v>
       </c>
       <c r="C15" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-19</v>
       </c>
       <c r="D15" t="str">
-        <v>Completed</v>
+        <v>Dropped</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-04-19</v>
+        <v/>
       </c>
       <c r="F15">
-        <v>7</v>
-      </c>
-      <c r="G15">
-        <v>94</v>
-      </c>
-      <c r="H15">
-        <v>4.4</v>
+        <v>13</v>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>AP0009</v>
+        <v>AP0013</v>
       </c>
       <c r="B16" t="str">
-        <v>LDP-003</v>
+        <v>LDP-008</v>
       </c>
       <c r="C16" t="str">
-        <v>2026-03-12</v>
+        <v>2026-05-05</v>
       </c>
       <c r="D16" t="str">
         <v>Completed</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F16">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G16">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="H16">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>AP0010</v>
+        <v>AP0014</v>
       </c>
       <c r="B17" t="str">
-        <v>LDP-006</v>
+        <v>LDP-005</v>
       </c>
       <c r="C17" t="str">
-        <v>2026-04-06</v>
+        <v>2026-05-02</v>
       </c>
       <c r="D17" t="str">
-        <v>Completed</v>
+        <v>Enrolled</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-04-26</v>
+        <v/>
       </c>
       <c r="F17">
-        <v>10</v>
-      </c>
-      <c r="G17">
-        <v>85</v>
-      </c>
-      <c r="H17">
-        <v>4.8</v>
+        <v>15</v>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>AP0010</v>
+        <v>AP0015</v>
       </c>
       <c r="B18" t="str">
-        <v>LDP-008</v>
+        <v>LDP-007</v>
       </c>
       <c r="C18" t="str">
-        <v>2026-05-04</v>
+        <v>2026-04-01</v>
       </c>
       <c r="D18" t="str">
-        <v>Dropped</v>
+        <v>Completed</v>
       </c>
       <c r="E18" t="str">
-        <v/>
+        <v>2026-04-20</v>
       </c>
       <c r="F18">
-        <v>11</v>
-      </c>
-      <c r="G18" t="str">
-        <v/>
-      </c>
-      <c r="H18" t="str">
-        <v/>
+        <v>6</v>
+      </c>
+      <c r="G18">
+        <v>93</v>
+      </c>
+      <c r="H18">
+        <v>4.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>AP0010</v>
+        <v>AP0017</v>
       </c>
       <c r="B19" t="str">
-        <v>LDP-003</v>
+        <v>LDP-001</v>
       </c>
       <c r="C19" t="str">
-        <v>2026-03-10</v>
+        <v>2026-05-17</v>
       </c>
       <c r="D19" t="str">
         <v>Completed</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-03</v>
       </c>
       <c r="F19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G19">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="H19">
-        <v>3</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>AP0012</v>
+        <v>AP0017</v>
       </c>
       <c r="B20" t="str">
-        <v>LDP-008</v>
+        <v>LDP-010</v>
       </c>
       <c r="C20" t="str">
         <v>2026-05-19</v>
       </c>
       <c r="D20" t="str">
-        <v>Completed</v>
+        <v>In-progress</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-05-04</v>
+        <v/>
       </c>
       <c r="F20">
-        <v>14</v>
-      </c>
-      <c r="G20">
-        <v>62</v>
-      </c>
-      <c r="H20">
-        <v>4.6</v>
+        <v>10</v>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>AP0012</v>
+        <v>AP0018</v>
       </c>
       <c r="B21" t="str">
-        <v>LDP-009</v>
+        <v>LDP-004</v>
       </c>
       <c r="C21" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-23</v>
       </c>
       <c r="D21" t="str">
         <v>Completed</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G21">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="H21">
         <v>4.9</v>
@@ -947,195 +947,195 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>AP0013</v>
+        <v>AP0019</v>
       </c>
       <c r="B22" t="str">
-        <v>LDP-001</v>
+        <v>LDP-003</v>
       </c>
       <c r="C22" t="str">
-        <v>2026-05-10</v>
+        <v>2026-03-10</v>
       </c>
       <c r="D22" t="str">
         <v>Completed</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-05</v>
       </c>
       <c r="F22">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G22">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H22">
-        <v>3.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>AP0013</v>
+        <v>AP0019</v>
       </c>
       <c r="B23" t="str">
-        <v>LDP-010</v>
+        <v>LDP-002</v>
       </c>
       <c r="C23" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-25</v>
       </c>
       <c r="D23" t="str">
-        <v>In-progress</v>
+        <v>Completed</v>
       </c>
       <c r="E23" t="str">
-        <v/>
+        <v>2026-05-08</v>
       </c>
       <c r="F23">
-        <v>8</v>
-      </c>
-      <c r="G23" t="str">
-        <v/>
-      </c>
-      <c r="H23" t="str">
-        <v/>
+        <v>4</v>
+      </c>
+      <c r="G23">
+        <v>59</v>
+      </c>
+      <c r="H23">
+        <v>4.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>AP0013</v>
+        <v>AP0019</v>
       </c>
       <c r="B24" t="str">
-        <v>LDP-008</v>
+        <v>LDP-004</v>
       </c>
       <c r="C24" t="str">
-        <v>2026-05-05</v>
+        <v>2026-03-13</v>
       </c>
       <c r="D24" t="str">
-        <v>Completed</v>
+        <v>Enrolled</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-05-18</v>
+        <v/>
       </c>
       <c r="F24">
-        <v>8</v>
-      </c>
-      <c r="G24">
-        <v>58</v>
-      </c>
-      <c r="H24">
-        <v>3.5</v>
+        <v>5</v>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>AP0014</v>
+        <v>AP0021</v>
       </c>
       <c r="B25" t="str">
-        <v>LDP-008</v>
+        <v>LDP-003</v>
       </c>
       <c r="C25" t="str">
-        <v>2026-04-05</v>
+        <v>2026-04-12</v>
       </c>
       <c r="D25" t="str">
-        <v>Dropped</v>
+        <v>Completed</v>
       </c>
       <c r="E25" t="str">
-        <v/>
+        <v>2026-04-19</v>
       </c>
       <c r="F25">
-        <v>3</v>
-      </c>
-      <c r="G25" t="str">
-        <v/>
-      </c>
-      <c r="H25" t="str">
-        <v/>
+        <v>16</v>
+      </c>
+      <c r="G25">
+        <v>68</v>
+      </c>
+      <c r="H25">
+        <v>3.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>AP0014</v>
+        <v>AP0021</v>
       </c>
       <c r="B26" t="str">
-        <v>LDP-005</v>
+        <v>LDP-006</v>
       </c>
       <c r="C26" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-22</v>
       </c>
       <c r="D26" t="str">
-        <v>Completed</v>
+        <v>Enrolled</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-05-27</v>
+        <v/>
       </c>
       <c r="F26">
-        <v>16</v>
-      </c>
-      <c r="G26">
-        <v>69</v>
-      </c>
-      <c r="H26">
-        <v>3.7</v>
+        <v>3</v>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>AP0016</v>
+        <v>AP0022</v>
       </c>
       <c r="B27" t="str">
-        <v>LDP-003</v>
+        <v>LDP-004</v>
       </c>
       <c r="C27" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-14</v>
       </c>
       <c r="D27" t="str">
         <v>Completed</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-04-05</v>
+        <v>2026-04-06</v>
       </c>
       <c r="F27">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="G27">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="H27">
-        <v>3</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>AP0016</v>
+        <v>AP0022</v>
       </c>
       <c r="B28" t="str">
         <v>LDP-002</v>
       </c>
       <c r="C28" t="str">
-        <v>2026-05-25</v>
+        <v>2026-04-21</v>
       </c>
       <c r="D28" t="str">
         <v>Completed</v>
       </c>
       <c r="E28" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-24</v>
       </c>
       <c r="F28">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G28">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="H28">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>AP0016</v>
+        <v>AP0023</v>
       </c>
       <c r="B29" t="str">
-        <v>LDP-004</v>
+        <v>LDP-005</v>
       </c>
       <c r="C29" t="str">
-        <v>2026-03-13</v>
+        <v>2026-04-03</v>
       </c>
       <c r="D29" t="str">
         <v>Enrolled</v>
@@ -1144,7 +1144,7 @@
         <v/>
       </c>
       <c r="F29">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1155,169 +1155,169 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>AP0017</v>
+        <v>AP0023</v>
       </c>
       <c r="B30" t="str">
-        <v>LDP-003</v>
+        <v>LDP-001</v>
       </c>
       <c r="C30" t="str">
-        <v>2026-04-12</v>
+        <v>2026-05-20</v>
       </c>
       <c r="D30" t="str">
         <v>Completed</v>
       </c>
       <c r="E30" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-11</v>
       </c>
       <c r="F30">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G30">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="H30">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>AP0017</v>
+        <v>AP0024</v>
       </c>
       <c r="B31" t="str">
-        <v>LDP-006</v>
+        <v>LDP-008</v>
       </c>
       <c r="C31" t="str">
-        <v>2026-04-22</v>
+        <v>2026-05-22</v>
       </c>
       <c r="D31" t="str">
-        <v>Enrolled</v>
+        <v>Completed</v>
       </c>
       <c r="E31" t="str">
-        <v/>
+        <v>2026-05-06</v>
       </c>
       <c r="F31">
-        <v>3</v>
-      </c>
-      <c r="G31" t="str">
-        <v/>
-      </c>
-      <c r="H31" t="str">
-        <v/>
+        <v>2</v>
+      </c>
+      <c r="G31">
+        <v>55</v>
+      </c>
+      <c r="H31">
+        <v>3.9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>AP0018</v>
+        <v>AP0024</v>
       </c>
       <c r="B32" t="str">
-        <v>LDP-004</v>
+        <v>LDP-005</v>
       </c>
       <c r="C32" t="str">
-        <v>2026-03-14</v>
+        <v>2026-03-23</v>
       </c>
       <c r="D32" t="str">
         <v>Completed</v>
       </c>
       <c r="E32" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-10</v>
       </c>
       <c r="F32">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G32">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="H32">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>AP0018</v>
+        <v>AP0025</v>
       </c>
       <c r="B33" t="str">
-        <v>LDP-002</v>
+        <v>LDP-008</v>
       </c>
       <c r="C33" t="str">
-        <v>2026-04-21</v>
+        <v>2026-05-19</v>
       </c>
       <c r="D33" t="str">
         <v>Completed</v>
       </c>
       <c r="E33" t="str">
-        <v>2026-05-24</v>
+        <v>2026-04-08</v>
       </c>
       <c r="F33">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G33">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="H33">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>AP0019</v>
+        <v>AP0025</v>
       </c>
       <c r="B34" t="str">
-        <v>LDP-005</v>
+        <v>LDP-007</v>
       </c>
       <c r="C34" t="str">
-        <v>2026-04-03</v>
+        <v>2026-04-16</v>
       </c>
       <c r="D34" t="str">
-        <v>Enrolled</v>
+        <v>Completed</v>
       </c>
       <c r="E34" t="str">
-        <v/>
+        <v>2026-04-05</v>
       </c>
       <c r="F34">
-        <v>10</v>
-      </c>
-      <c r="G34" t="str">
-        <v/>
-      </c>
-      <c r="H34" t="str">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="G34">
+        <v>81</v>
+      </c>
+      <c r="H34">
+        <v>4.4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>AP0019</v>
+        <v>AP0025</v>
       </c>
       <c r="B35" t="str">
         <v>LDP-001</v>
       </c>
       <c r="C35" t="str">
-        <v>2026-05-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="D35" t="str">
         <v>Completed</v>
       </c>
       <c r="E35" t="str">
-        <v>2026-04-11</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F35">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G35">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="H35">
-        <v>3.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>AP0021</v>
+        <v>AP0026</v>
       </c>
       <c r="B36" t="str">
-        <v>LDP-008</v>
+        <v>LDP-003</v>
       </c>
       <c r="C36" t="str">
-        <v>2026-05-22</v>
+        <v>2026-04-02</v>
       </c>
       <c r="D36" t="str">
         <v>Completed</v>
@@ -1326,284 +1326,284 @@
         <v>2026-05-06</v>
       </c>
       <c r="F36">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="G36">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="H36">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>AP0021</v>
+        <v>AP0026</v>
       </c>
       <c r="B37" t="str">
         <v>LDP-005</v>
       </c>
       <c r="C37" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-05</v>
       </c>
       <c r="D37" t="str">
         <v>Completed</v>
       </c>
       <c r="E37" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-18</v>
       </c>
       <c r="F37">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G37">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="H37">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>AP0022</v>
+        <v>AP0027</v>
       </c>
       <c r="B38" t="str">
-        <v>LDP-008</v>
+        <v>LDP-006</v>
       </c>
       <c r="C38" t="str">
-        <v>2026-05-19</v>
+        <v>2026-03-14</v>
       </c>
       <c r="D38" t="str">
         <v>Completed</v>
       </c>
       <c r="E38" t="str">
-        <v>2026-04-08</v>
+        <v>2026-05-06</v>
       </c>
       <c r="F38">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="G38">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="H38">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>AP0022</v>
+        <v>AP0027</v>
       </c>
       <c r="B39" t="str">
-        <v>LDP-007</v>
+        <v>LDP-009</v>
       </c>
       <c r="C39" t="str">
-        <v>2026-04-16</v>
+        <v>2026-03-23</v>
       </c>
       <c r="D39" t="str">
-        <v>Completed</v>
+        <v>In-progress</v>
       </c>
       <c r="E39" t="str">
-        <v>2026-04-05</v>
+        <v/>
       </c>
       <c r="F39">
-        <v>3</v>
-      </c>
-      <c r="G39">
-        <v>81</v>
-      </c>
-      <c r="H39">
-        <v>4.4</v>
+        <v>13</v>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>AP0022</v>
+        <v>AP0028</v>
       </c>
       <c r="B40" t="str">
-        <v>LDP-001</v>
+        <v>LDP-008</v>
       </c>
       <c r="C40" t="str">
-        <v>2026-03-21</v>
+        <v>2026-03-13</v>
       </c>
       <c r="D40" t="str">
         <v>Completed</v>
       </c>
       <c r="E40" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-07</v>
       </c>
       <c r="F40">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G40">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="H40">
-        <v>4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>AP0023</v>
+        <v>AP0029</v>
       </c>
       <c r="B41" t="str">
-        <v>LDP-003</v>
+        <v>LDP-008</v>
       </c>
       <c r="C41" t="str">
-        <v>2026-04-02</v>
+        <v>2026-05-24</v>
       </c>
       <c r="D41" t="str">
         <v>Completed</v>
       </c>
       <c r="E41" t="str">
-        <v>2026-05-06</v>
+        <v>2026-04-15</v>
       </c>
       <c r="F41">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G41">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="H41">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>AP0023</v>
+        <v>AP0030</v>
       </c>
       <c r="B42" t="str">
-        <v>LDP-005</v>
+        <v>LDP-009</v>
       </c>
       <c r="C42" t="str">
-        <v>2026-03-05</v>
+        <v>2026-04-05</v>
       </c>
       <c r="D42" t="str">
-        <v>Completed</v>
+        <v>In-progress</v>
       </c>
       <c r="E42" t="str">
-        <v>2026-04-18</v>
+        <v/>
       </c>
       <c r="F42">
-        <v>8</v>
-      </c>
-      <c r="G42">
-        <v>58</v>
-      </c>
-      <c r="H42">
-        <v>3.9</v>
+        <v>5</v>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>AP0024</v>
+        <v>AP0030</v>
       </c>
       <c r="B43" t="str">
-        <v>LDP-006</v>
+        <v>LDP-003</v>
       </c>
       <c r="C43" t="str">
-        <v>2026-03-14</v>
+        <v>2026-03-17</v>
       </c>
       <c r="D43" t="str">
         <v>Completed</v>
       </c>
       <c r="E43" t="str">
-        <v>2026-05-06</v>
+        <v>2026-04-27</v>
       </c>
       <c r="F43">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G43">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H43">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>AP0024</v>
+        <v>AP0033</v>
       </c>
       <c r="B44" t="str">
-        <v>LDP-009</v>
+        <v>LDP-001</v>
       </c>
       <c r="C44" t="str">
-        <v>2026-03-23</v>
+        <v>2026-04-03</v>
       </c>
       <c r="D44" t="str">
-        <v>In-progress</v>
+        <v>Completed</v>
       </c>
       <c r="E44" t="str">
-        <v/>
+        <v>2026-04-22</v>
       </c>
       <c r="F44">
-        <v>13</v>
-      </c>
-      <c r="G44" t="str">
-        <v/>
-      </c>
-      <c r="H44" t="str">
-        <v/>
+        <v>8</v>
+      </c>
+      <c r="G44">
+        <v>74</v>
+      </c>
+      <c r="H44">
+        <v>3.6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>AP0025</v>
+        <v>AP0034</v>
       </c>
       <c r="B45" t="str">
-        <v>LDP-008</v>
+        <v>LDP-001</v>
       </c>
       <c r="C45" t="str">
-        <v>2026-03-13</v>
+        <v>2026-03-01</v>
       </c>
       <c r="D45" t="str">
         <v>Completed</v>
       </c>
       <c r="E45" t="str">
-        <v>2026-05-07</v>
+        <v>2026-05-17</v>
       </c>
       <c r="F45">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G45">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="H45">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>AP0026</v>
+        <v>AP0034</v>
       </c>
       <c r="B46" t="str">
-        <v>LDP-008</v>
+        <v>LDP-004</v>
       </c>
       <c r="C46" t="str">
-        <v>2026-05-24</v>
+        <v>2026-04-10</v>
       </c>
       <c r="D46" t="str">
         <v>Completed</v>
       </c>
       <c r="E46" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="F46">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G46">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="H46">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>AP0027</v>
+        <v>AP0034</v>
       </c>
       <c r="B47" t="str">
-        <v>LDP-009</v>
+        <v>LDP-010</v>
       </c>
       <c r="C47" t="str">
-        <v>2026-04-05</v>
+        <v>2026-05-17</v>
       </c>
       <c r="D47" t="str">
         <v>In-progress</v>
@@ -1612,7 +1612,7 @@
         <v/>
       </c>
       <c r="F47">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -1623,152 +1623,152 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>AP0027</v>
+        <v>AP0035</v>
       </c>
       <c r="B48" t="str">
-        <v>LDP-003</v>
+        <v>LDP-007</v>
       </c>
       <c r="C48" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-10</v>
       </c>
       <c r="D48" t="str">
-        <v>Completed</v>
+        <v>In-progress</v>
       </c>
       <c r="E48" t="str">
-        <v>2026-04-27</v>
+        <v/>
       </c>
       <c r="F48">
-        <v>12</v>
-      </c>
-      <c r="G48">
-        <v>69</v>
-      </c>
-      <c r="H48">
-        <v>4.7</v>
+        <v>7</v>
+      </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
+      <c r="H48" t="str">
+        <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>AP0029</v>
+        <v>AP0035</v>
       </c>
       <c r="B49" t="str">
-        <v>LDP-001</v>
+        <v>LDP-006</v>
       </c>
       <c r="C49" t="str">
-        <v>2026-04-03</v>
+        <v>2026-04-20</v>
       </c>
       <c r="D49" t="str">
-        <v>Completed</v>
+        <v>Enrolled</v>
       </c>
       <c r="E49" t="str">
-        <v>2026-04-22</v>
+        <v/>
       </c>
       <c r="F49">
-        <v>8</v>
-      </c>
-      <c r="G49">
-        <v>74</v>
-      </c>
-      <c r="H49">
-        <v>3.6</v>
+        <v>14</v>
+      </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
+      <c r="H49" t="str">
+        <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>AP0030</v>
+        <v>AP0042</v>
       </c>
       <c r="B50" t="str">
         <v>LDP-001</v>
       </c>
       <c r="C50" t="str">
-        <v>2026-03-01</v>
+        <v>2026-04-01</v>
       </c>
       <c r="D50" t="str">
         <v>Completed</v>
       </c>
       <c r="E50" t="str">
-        <v>2026-05-17</v>
+        <v>2026-04-15</v>
       </c>
       <c r="F50">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G50">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="H50">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>AP0030</v>
+        <v>AP0045</v>
       </c>
       <c r="B51" t="str">
-        <v>LDP-004</v>
+        <v>LDP-008</v>
       </c>
       <c r="C51" t="str">
-        <v>2026-04-10</v>
+        <v>2026-05-16</v>
       </c>
       <c r="D51" t="str">
         <v>Completed</v>
       </c>
       <c r="E51" t="str">
-        <v>2026-04-16</v>
+        <v>2026-05-12</v>
       </c>
       <c r="F51">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G51">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="H51">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>AP0030</v>
+        <v>AP0048</v>
       </c>
       <c r="B52" t="str">
-        <v>LDP-010</v>
+        <v>LDP-002</v>
       </c>
       <c r="C52" t="str">
-        <v>2026-05-17</v>
+        <v>2026-04-03</v>
       </c>
       <c r="D52" t="str">
-        <v>In-progress</v>
+        <v>Completed</v>
       </c>
       <c r="E52" t="str">
-        <v/>
+        <v>2026-04-28</v>
       </c>
       <c r="F52">
-        <v>16</v>
-      </c>
-      <c r="G52" t="str">
-        <v/>
-      </c>
-      <c r="H52" t="str">
-        <v/>
+        <v>9</v>
+      </c>
+      <c r="G52">
+        <v>73</v>
+      </c>
+      <c r="H52">
+        <v>4.2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>AP0031</v>
+        <v>AP0048</v>
       </c>
       <c r="B53" t="str">
-        <v>LDP-007</v>
+        <v>LDP-003</v>
       </c>
       <c r="C53" t="str">
-        <v>2026-03-10</v>
+        <v>2026-05-12</v>
       </c>
       <c r="D53" t="str">
-        <v>In-progress</v>
+        <v>Enrolled</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -1779,22 +1779,22 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>AP0031</v>
+        <v>AP0050</v>
       </c>
       <c r="B54" t="str">
-        <v>LDP-006</v>
+        <v>LDP-009</v>
       </c>
       <c r="C54" t="str">
-        <v>2026-04-20</v>
+        <v>2026-05-24</v>
       </c>
       <c r="D54" t="str">
-        <v>Enrolled</v>
+        <v>In-progress</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -1805,244 +1805,244 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>AP0033</v>
+        <v>AP0050</v>
       </c>
       <c r="B55" t="str">
-        <v>LDP-010</v>
+        <v>LDP-006</v>
       </c>
       <c r="C55" t="str">
-        <v>2026-03-02</v>
+        <v>2026-04-02</v>
       </c>
       <c r="D55" t="str">
-        <v>Completed</v>
+        <v>Dropped</v>
       </c>
       <c r="E55" t="str">
-        <v>2026-04-18</v>
+        <v/>
       </c>
       <c r="F55">
-        <v>2</v>
-      </c>
-      <c r="G55">
-        <v>75</v>
-      </c>
-      <c r="H55">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="G55" t="str">
+        <v/>
+      </c>
+      <c r="H55" t="str">
+        <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>AP0033</v>
+        <v>AP0056</v>
       </c>
       <c r="B56" t="str">
-        <v>LDP-008</v>
+        <v>LDP-006</v>
       </c>
       <c r="C56" t="str">
-        <v>2026-04-24</v>
+        <v>2026-03-20</v>
       </c>
       <c r="D56" t="str">
         <v>Completed</v>
       </c>
       <c r="E56" t="str">
-        <v>2026-05-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="F56">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G56">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H56">
-        <v>3.8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>AP0033</v>
+        <v>AP0056</v>
       </c>
       <c r="B57" t="str">
-        <v>LDP-009</v>
+        <v>LDP-003</v>
       </c>
       <c r="C57" t="str">
-        <v>2026-05-11</v>
+        <v>2026-03-02</v>
       </c>
       <c r="D57" t="str">
-        <v>In-progress</v>
+        <v>Completed</v>
       </c>
       <c r="E57" t="str">
-        <v/>
+        <v>2026-04-25</v>
       </c>
       <c r="F57">
-        <v>4</v>
-      </c>
-      <c r="G57" t="str">
-        <v/>
-      </c>
-      <c r="H57" t="str">
-        <v/>
+        <v>12</v>
+      </c>
+      <c r="G57">
+        <v>96</v>
+      </c>
+      <c r="H57">
+        <v>3.4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>AP0039</v>
+        <v>AP0059</v>
       </c>
       <c r="B58" t="str">
-        <v>LDP-002</v>
+        <v>LDP-008</v>
       </c>
       <c r="C58" t="str">
-        <v>2026-04-03</v>
+        <v>2026-05-10</v>
       </c>
       <c r="D58" t="str">
         <v>Completed</v>
       </c>
       <c r="E58" t="str">
-        <v>2026-04-28</v>
+        <v>2026-05-12</v>
       </c>
       <c r="F58">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G58">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="H58">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>AP0039</v>
+        <v>AP0059</v>
       </c>
       <c r="B59" t="str">
-        <v>LDP-003</v>
+        <v>LDP-002</v>
       </c>
       <c r="C59" t="str">
-        <v>2026-05-12</v>
+        <v>2026-04-02</v>
       </c>
       <c r="D59" t="str">
-        <v>Enrolled</v>
+        <v>Completed</v>
       </c>
       <c r="E59" t="str">
-        <v/>
+        <v>2026-05-20</v>
       </c>
       <c r="F59">
-        <v>9</v>
-      </c>
-      <c r="G59" t="str">
-        <v/>
-      </c>
-      <c r="H59" t="str">
-        <v/>
+        <v>12</v>
+      </c>
+      <c r="G59">
+        <v>69</v>
+      </c>
+      <c r="H59">
+        <v>4.6</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>AP0040</v>
+        <v>AP0064</v>
       </c>
       <c r="B60" t="str">
-        <v>LDP-009</v>
+        <v>LDP-008</v>
       </c>
       <c r="C60" t="str">
-        <v>2026-05-24</v>
+        <v>2026-03-22</v>
       </c>
       <c r="D60" t="str">
-        <v>In-progress</v>
+        <v>Completed</v>
       </c>
       <c r="E60" t="str">
-        <v/>
+        <v>2026-04-03</v>
       </c>
       <c r="F60">
-        <v>7</v>
-      </c>
-      <c r="G60" t="str">
-        <v/>
-      </c>
-      <c r="H60" t="str">
-        <v/>
+        <v>13</v>
+      </c>
+      <c r="G60">
+        <v>58</v>
+      </c>
+      <c r="H60">
+        <v>4.8</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>AP0040</v>
+        <v>AP0065</v>
       </c>
       <c r="B61" t="str">
-        <v>LDP-006</v>
+        <v>LDP-005</v>
       </c>
       <c r="C61" t="str">
-        <v>2026-04-02</v>
+        <v>2026-05-05</v>
       </c>
       <c r="D61" t="str">
-        <v>Dropped</v>
+        <v>Completed</v>
       </c>
       <c r="E61" t="str">
-        <v/>
+        <v>2026-04-24</v>
       </c>
       <c r="F61">
-        <v>5</v>
-      </c>
-      <c r="G61" t="str">
-        <v/>
-      </c>
-      <c r="H61" t="str">
-        <v/>
+        <v>4</v>
+      </c>
+      <c r="G61">
+        <v>95</v>
+      </c>
+      <c r="H61">
+        <v>4.2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>AP0047</v>
+        <v>AP0068</v>
       </c>
       <c r="B62" t="str">
-        <v>LDP-006</v>
+        <v>LDP-009</v>
       </c>
       <c r="C62" t="str">
-        <v>2026-03-20</v>
+        <v>2026-05-13</v>
       </c>
       <c r="D62" t="str">
         <v>Completed</v>
       </c>
       <c r="E62" t="str">
-        <v>2026-04-09</v>
+        <v>2026-05-02</v>
       </c>
       <c r="F62">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G62">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="H62">
-        <v>4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>AP0047</v>
+        <v>AP0068</v>
       </c>
       <c r="B63" t="str">
-        <v>LDP-003</v>
+        <v>LDP-005</v>
       </c>
       <c r="C63" t="str">
-        <v>2026-03-02</v>
+        <v>2026-04-25</v>
       </c>
       <c r="D63" t="str">
-        <v>Completed</v>
+        <v>Enrolled</v>
       </c>
       <c r="E63" t="str">
-        <v>2026-04-25</v>
+        <v/>
       </c>
       <c r="F63">
-        <v>12</v>
-      </c>
-      <c r="G63">
-        <v>96</v>
-      </c>
-      <c r="H63">
-        <v>3.4</v>
+        <v>15</v>
+      </c>
+      <c r="G63" t="str">
+        <v/>
+      </c>
+      <c r="H63" t="str">
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>AP0051</v>
+        <v>AP0068</v>
       </c>
       <c r="B64" t="str">
-        <v>LDP-008</v>
+        <v>LDP-001</v>
       </c>
       <c r="C64" t="str">
         <v>2026-05-10</v>
@@ -2051,91 +2051,91 @@
         <v>Completed</v>
       </c>
       <c r="E64" t="str">
-        <v>2026-05-12</v>
+        <v>2026-04-25</v>
       </c>
       <c r="F64">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G64">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H64">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>AP0051</v>
+        <v>AP0069</v>
       </c>
       <c r="B65" t="str">
-        <v>LDP-002</v>
+        <v>LDP-005</v>
       </c>
       <c r="C65" t="str">
-        <v>2026-04-02</v>
+        <v>2026-03-06</v>
       </c>
       <c r="D65" t="str">
         <v>Completed</v>
       </c>
       <c r="E65" t="str">
-        <v>2026-05-20</v>
+        <v>2026-04-04</v>
       </c>
       <c r="F65">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G65">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="H65">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>AP0055</v>
+        <v>AP0069</v>
       </c>
       <c r="B66" t="str">
-        <v>LDP-008</v>
+        <v>LDP-004</v>
       </c>
       <c r="C66" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-10</v>
       </c>
       <c r="D66" t="str">
-        <v>Completed</v>
+        <v>In-progress</v>
       </c>
       <c r="E66" t="str">
-        <v>2026-04-03</v>
+        <v/>
       </c>
       <c r="F66">
-        <v>13</v>
-      </c>
-      <c r="G66">
-        <v>58</v>
-      </c>
-      <c r="H66">
-        <v>4.8</v>
+        <v>11</v>
+      </c>
+      <c r="G66" t="str">
+        <v/>
+      </c>
+      <c r="H66" t="str">
+        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>AP0056</v>
+        <v>AP0070</v>
       </c>
       <c r="B67" t="str">
-        <v>LDP-005</v>
+        <v>LDP-010</v>
       </c>
       <c r="C67" t="str">
-        <v>2026-05-05</v>
+        <v>2026-04-19</v>
       </c>
       <c r="D67" t="str">
         <v>Completed</v>
       </c>
       <c r="E67" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-19</v>
       </c>
       <c r="F67">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G67">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H67">
         <v>4.2</v>
@@ -2143,25 +2143,25 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>AP0059</v>
+        <v>AP0070</v>
       </c>
       <c r="B68" t="str">
-        <v>LDP-009</v>
+        <v>LDP-001</v>
       </c>
       <c r="C68" t="str">
-        <v>2026-05-13</v>
+        <v>2026-03-21</v>
       </c>
       <c r="D68" t="str">
         <v>Completed</v>
       </c>
       <c r="E68" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-19</v>
       </c>
       <c r="F68">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G68">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="H68">
         <v>3.6</v>
@@ -2169,100 +2169,100 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>AP0059</v>
+        <v>AP0073</v>
       </c>
       <c r="B69" t="str">
-        <v>LDP-005</v>
+        <v>LDP-010</v>
       </c>
       <c r="C69" t="str">
-        <v>2026-04-25</v>
+        <v>2026-04-10</v>
       </c>
       <c r="D69" t="str">
-        <v>Enrolled</v>
+        <v>Completed</v>
       </c>
       <c r="E69" t="str">
-        <v/>
+        <v>2026-05-20</v>
       </c>
       <c r="F69">
-        <v>15</v>
-      </c>
-      <c r="G69" t="str">
-        <v/>
-      </c>
-      <c r="H69" t="str">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="G69">
+        <v>87</v>
+      </c>
+      <c r="H69">
+        <v>3.9</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>AP0059</v>
+        <v>AP0073</v>
       </c>
       <c r="B70" t="str">
-        <v>LDP-001</v>
+        <v>LDP-005</v>
       </c>
       <c r="C70" t="str">
-        <v>2026-05-10</v>
+        <v>2026-03-16</v>
       </c>
       <c r="D70" t="str">
-        <v>Completed</v>
+        <v>Enrolled</v>
       </c>
       <c r="E70" t="str">
-        <v>2026-04-25</v>
+        <v/>
       </c>
       <c r="F70">
-        <v>16</v>
-      </c>
-      <c r="G70">
-        <v>86</v>
-      </c>
-      <c r="H70">
-        <v>4.5</v>
+        <v>13</v>
+      </c>
+      <c r="G70" t="str">
+        <v/>
+      </c>
+      <c r="H70" t="str">
+        <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>AP0060</v>
+        <v>AP0076</v>
       </c>
       <c r="B71" t="str">
-        <v>LDP-005</v>
+        <v>LDP-001</v>
       </c>
       <c r="C71" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-16</v>
       </c>
       <c r="D71" t="str">
         <v>Completed</v>
       </c>
       <c r="E71" t="str">
-        <v>2026-04-04</v>
+        <v>2026-05-19</v>
       </c>
       <c r="F71">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G71">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="H71">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>AP0060</v>
+        <v>AP0076</v>
       </c>
       <c r="B72" t="str">
         <v>LDP-004</v>
       </c>
       <c r="C72" t="str">
-        <v>2026-03-10</v>
+        <v>2026-05-22</v>
       </c>
       <c r="D72" t="str">
-        <v>In-progress</v>
+        <v>Enrolled</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -2273,39 +2273,39 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>AP0061</v>
+        <v>AP0076</v>
       </c>
       <c r="B73" t="str">
-        <v>LDP-010</v>
+        <v>LDP-002</v>
       </c>
       <c r="C73" t="str">
-        <v>2026-04-19</v>
+        <v>2026-03-05</v>
       </c>
       <c r="D73" t="str">
         <v>Completed</v>
       </c>
       <c r="E73" t="str">
-        <v>2026-04-19</v>
+        <v>2026-05-21</v>
       </c>
       <c r="F73">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G73">
         <v>84</v>
       </c>
       <c r="H73">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>AP0061</v>
+        <v>AP0077</v>
       </c>
       <c r="B74" t="str">
-        <v>LDP-001</v>
+        <v>LDP-004</v>
       </c>
       <c r="C74" t="str">
-        <v>2026-03-21</v>
+        <v>2026-04-24</v>
       </c>
       <c r="D74" t="str">
         <v>Completed</v>
@@ -2314,183 +2314,183 @@
         <v>2026-05-19</v>
       </c>
       <c r="F74">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G74">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="H74">
-        <v>3.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>AP0065</v>
+        <v>AP0077</v>
       </c>
       <c r="B75" t="str">
-        <v>LDP-010</v>
+        <v>LDP-001</v>
       </c>
       <c r="C75" t="str">
-        <v>2026-04-10</v>
+        <v>2026-03-21</v>
       </c>
       <c r="D75" t="str">
-        <v>Completed</v>
+        <v>Dropped</v>
       </c>
       <c r="E75" t="str">
-        <v>2026-05-20</v>
+        <v/>
       </c>
       <c r="F75">
-        <v>3</v>
-      </c>
-      <c r="G75">
-        <v>87</v>
-      </c>
-      <c r="H75">
-        <v>3.9</v>
+        <v>16</v>
+      </c>
+      <c r="G75" t="str">
+        <v/>
+      </c>
+      <c r="H75" t="str">
+        <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>AP0065</v>
+        <v>AP0077</v>
       </c>
       <c r="B76" t="str">
         <v>LDP-005</v>
       </c>
       <c r="C76" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-22</v>
       </c>
       <c r="D76" t="str">
-        <v>Enrolled</v>
+        <v>Completed</v>
       </c>
       <c r="E76" t="str">
-        <v/>
+        <v>2026-04-06</v>
       </c>
       <c r="F76">
-        <v>13</v>
-      </c>
-      <c r="G76" t="str">
-        <v/>
-      </c>
-      <c r="H76" t="str">
-        <v/>
+        <v>7</v>
+      </c>
+      <c r="G76">
+        <v>58</v>
+      </c>
+      <c r="H76">
+        <v>4.9</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>AP0068</v>
+        <v>AP0080</v>
       </c>
       <c r="B77" t="str">
-        <v>LDP-001</v>
+        <v>LDP-002</v>
       </c>
       <c r="C77" t="str">
-        <v>2026-03-16</v>
+        <v>2026-04-08</v>
       </c>
       <c r="D77" t="str">
         <v>Completed</v>
       </c>
       <c r="E77" t="str">
-        <v>2026-05-19</v>
+        <v>2026-04-01</v>
       </c>
       <c r="F77">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G77">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="H77">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>AP0068</v>
+        <v>AP0081</v>
       </c>
       <c r="B78" t="str">
-        <v>LDP-004</v>
+        <v>LDP-002</v>
       </c>
       <c r="C78" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-11</v>
       </c>
       <c r="D78" t="str">
-        <v>Enrolled</v>
+        <v>Completed</v>
       </c>
       <c r="E78" t="str">
-        <v/>
+        <v>2026-04-16</v>
       </c>
       <c r="F78">
-        <v>7</v>
-      </c>
-      <c r="G78" t="str">
-        <v/>
-      </c>
-      <c r="H78" t="str">
-        <v/>
+        <v>4</v>
+      </c>
+      <c r="G78">
+        <v>66</v>
+      </c>
+      <c r="H78">
+        <v>3.6</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>AP0068</v>
+        <v>AP0081</v>
       </c>
       <c r="B79" t="str">
-        <v>LDP-002</v>
+        <v>LDP-004</v>
       </c>
       <c r="C79" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-12</v>
       </c>
       <c r="D79" t="str">
         <v>Completed</v>
       </c>
       <c r="E79" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-10</v>
       </c>
       <c r="F79">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G79">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="H79">
-        <v>4.8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>AP0069</v>
+        <v>AP0084</v>
       </c>
       <c r="B80" t="str">
-        <v>LDP-004</v>
+        <v>LDP-007</v>
       </c>
       <c r="C80" t="str">
-        <v>2026-04-24</v>
+        <v>2026-03-02</v>
       </c>
       <c r="D80" t="str">
         <v>Completed</v>
       </c>
       <c r="E80" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-17</v>
       </c>
       <c r="F80">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G80">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H80">
-        <v>5</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>AP0069</v>
+        <v>AP0084</v>
       </c>
       <c r="B81" t="str">
-        <v>LDP-001</v>
+        <v>LDP-003</v>
       </c>
       <c r="C81" t="str">
-        <v>2026-03-21</v>
+        <v>2026-03-09</v>
       </c>
       <c r="D81" t="str">
-        <v>Dropped</v>
+        <v>Enrolled</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -2507,273 +2507,273 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>AP0069</v>
+        <v>AP0086</v>
       </c>
       <c r="B82" t="str">
-        <v>LDP-005</v>
+        <v>LDP-003</v>
       </c>
       <c r="C82" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-21</v>
       </c>
       <c r="D82" t="str">
         <v>Completed</v>
       </c>
       <c r="E82" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-12</v>
       </c>
       <c r="F82">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G82">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="H82">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>AP0072</v>
+        <v>AP0086</v>
       </c>
       <c r="B83" t="str">
-        <v>LDP-002</v>
+        <v>LDP-009</v>
       </c>
       <c r="C83" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-10</v>
       </c>
       <c r="D83" t="str">
         <v>Completed</v>
       </c>
       <c r="E83" t="str">
-        <v>2026-04-01</v>
+        <v>2026-05-15</v>
       </c>
       <c r="F83">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G83">
         <v>97</v>
       </c>
       <c r="H83">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>AP0073</v>
+        <v>AP0089</v>
       </c>
       <c r="B84" t="str">
-        <v>LDP-002</v>
+        <v>LDP-007</v>
       </c>
       <c r="C84" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-14</v>
       </c>
       <c r="D84" t="str">
         <v>Completed</v>
       </c>
       <c r="E84" t="str">
-        <v>2026-04-16</v>
+        <v>2026-05-24</v>
       </c>
       <c r="F84">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G84">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="H84">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>AP0073</v>
+        <v>AP0089</v>
       </c>
       <c r="B85" t="str">
-        <v>LDP-004</v>
+        <v>LDP-010</v>
       </c>
       <c r="C85" t="str">
-        <v>2026-03-12</v>
+        <v>2026-03-23</v>
       </c>
       <c r="D85" t="str">
-        <v>Completed</v>
+        <v>In-progress</v>
       </c>
       <c r="E85" t="str">
-        <v>2026-05-10</v>
+        <v/>
       </c>
       <c r="F85">
-        <v>8</v>
-      </c>
-      <c r="G85">
-        <v>59</v>
-      </c>
-      <c r="H85">
-        <v>5</v>
+        <v>15</v>
+      </c>
+      <c r="G85" t="str">
+        <v/>
+      </c>
+      <c r="H85" t="str">
+        <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>AP0076</v>
+        <v>AP0090</v>
       </c>
       <c r="B86" t="str">
-        <v>LDP-007</v>
+        <v>LDP-010</v>
       </c>
       <c r="C86" t="str">
-        <v>2026-03-02</v>
+        <v>2026-05-01</v>
       </c>
       <c r="D86" t="str">
-        <v>Completed</v>
+        <v>Dropped</v>
       </c>
       <c r="E86" t="str">
-        <v>2026-05-17</v>
+        <v/>
       </c>
       <c r="F86">
-        <v>7</v>
-      </c>
-      <c r="G86">
-        <v>83</v>
-      </c>
-      <c r="H86">
-        <v>4.6</v>
+        <v>12</v>
+      </c>
+      <c r="G86" t="str">
+        <v/>
+      </c>
+      <c r="H86" t="str">
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>AP0076</v>
+        <v>AP0091</v>
       </c>
       <c r="B87" t="str">
-        <v>LDP-003</v>
+        <v>LDP-004</v>
       </c>
       <c r="C87" t="str">
-        <v>2026-03-09</v>
+        <v>2026-03-24</v>
       </c>
       <c r="D87" t="str">
-        <v>Enrolled</v>
+        <v>Completed</v>
       </c>
       <c r="E87" t="str">
-        <v/>
+        <v>2026-05-10</v>
       </c>
       <c r="F87">
-        <v>16</v>
-      </c>
-      <c r="G87" t="str">
-        <v/>
-      </c>
-      <c r="H87" t="str">
-        <v/>
+        <v>15</v>
+      </c>
+      <c r="G87">
+        <v>56</v>
+      </c>
+      <c r="H87">
+        <v>5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>AP0078</v>
+        <v>AP0091</v>
       </c>
       <c r="B88" t="str">
-        <v>LDP-003</v>
+        <v>LDP-010</v>
       </c>
       <c r="C88" t="str">
-        <v>2026-03-21</v>
+        <v>2026-04-10</v>
       </c>
       <c r="D88" t="str">
         <v>Completed</v>
       </c>
       <c r="E88" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-27</v>
       </c>
       <c r="F88">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G88">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="H88">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>AP0078</v>
+        <v>AP0095</v>
       </c>
       <c r="B89" t="str">
         <v>LDP-009</v>
       </c>
       <c r="C89" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-13</v>
       </c>
       <c r="D89" t="str">
         <v>Completed</v>
       </c>
       <c r="E89" t="str">
-        <v>2026-05-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="F89">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G89">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="H89">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>AP0084</v>
+        <v>AP0095</v>
       </c>
       <c r="B90" t="str">
-        <v>LDP-006</v>
+        <v>LDP-008</v>
       </c>
       <c r="C90" t="str">
-        <v>2026-04-11</v>
+        <v>2026-05-05</v>
       </c>
       <c r="D90" t="str">
         <v>Completed</v>
       </c>
       <c r="E90" t="str">
-        <v>2026-05-11</v>
+        <v>2026-04-16</v>
       </c>
       <c r="F90">
         <v>3</v>
       </c>
       <c r="G90">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="H90">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>AP0084</v>
+        <v>AP0096</v>
       </c>
       <c r="B91" t="str">
-        <v>LDP-008</v>
+        <v>LDP-010</v>
       </c>
       <c r="C91" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-03</v>
       </c>
       <c r="D91" t="str">
-        <v>Completed</v>
+        <v>In-progress</v>
       </c>
       <c r="E91" t="str">
-        <v>2026-05-22</v>
+        <v/>
       </c>
       <c r="F91">
-        <v>15</v>
-      </c>
-      <c r="G91">
-        <v>92</v>
-      </c>
-      <c r="H91">
-        <v>3</v>
+        <v>10</v>
+      </c>
+      <c r="G91" t="str">
+        <v/>
+      </c>
+      <c r="H91" t="str">
+        <v/>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>AP0084</v>
+        <v>AP0096</v>
       </c>
       <c r="B92" t="str">
-        <v>LDP-009</v>
+        <v>LDP-008</v>
       </c>
       <c r="C92" t="str">
-        <v>2026-04-10</v>
+        <v>2026-05-17</v>
       </c>
       <c r="D92" t="str">
         <v>In-progress</v>
@@ -2782,7 +2782,7 @@
         <v/>
       </c>
       <c r="F92">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -2793,181 +2793,181 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>AP0085</v>
+        <v>AP0097</v>
       </c>
       <c r="B93" t="str">
-        <v>LDP-010</v>
+        <v>LDP-009</v>
       </c>
       <c r="C93" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-11</v>
       </c>
       <c r="D93" t="str">
         <v>Completed</v>
       </c>
       <c r="E93" t="str">
-        <v>2026-04-28</v>
+        <v>2026-04-21</v>
       </c>
       <c r="F93">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G93">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H93">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>AP0086</v>
+        <v>AP0097</v>
       </c>
       <c r="B94" t="str">
-        <v>LDP-008</v>
+        <v>LDP-001</v>
       </c>
       <c r="C94" t="str">
-        <v>2026-04-13</v>
+        <v>2026-03-07</v>
       </c>
       <c r="D94" t="str">
-        <v>Dropped</v>
+        <v>Completed</v>
       </c>
       <c r="E94" t="str">
-        <v/>
+        <v>2026-04-07</v>
       </c>
       <c r="F94">
-        <v>14</v>
-      </c>
-      <c r="G94" t="str">
-        <v/>
-      </c>
-      <c r="H94" t="str">
-        <v/>
+        <v>2</v>
+      </c>
+      <c r="G94">
+        <v>69</v>
+      </c>
+      <c r="H94">
+        <v>4.3</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>AP0086</v>
+        <v>AP0098</v>
       </c>
       <c r="B95" t="str">
         <v>LDP-001</v>
       </c>
       <c r="C95" t="str">
-        <v>2026-03-13</v>
+        <v>2026-04-15</v>
       </c>
       <c r="D95" t="str">
         <v>Completed</v>
       </c>
       <c r="E95" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-08</v>
       </c>
       <c r="F95">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G95">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="H95">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>AP0089</v>
+        <v>AP0098</v>
       </c>
       <c r="B96" t="str">
-        <v>LDP-002</v>
+        <v>LDP-003</v>
       </c>
       <c r="C96" t="str">
-        <v>2026-04-11</v>
+        <v>2026-03-08</v>
       </c>
       <c r="D96" t="str">
         <v>Completed</v>
       </c>
       <c r="E96" t="str">
-        <v>2026-04-17</v>
+        <v>2026-05-20</v>
       </c>
       <c r="F96">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G96">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="H96">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>AP0089</v>
+        <v>AP0098</v>
       </c>
       <c r="B97" t="str">
-        <v>LDP-003</v>
+        <v>LDP-006</v>
       </c>
       <c r="C97" t="str">
-        <v>2026-04-03</v>
+        <v>2026-04-07</v>
       </c>
       <c r="D97" t="str">
         <v>Completed</v>
       </c>
       <c r="E97" t="str">
-        <v>2026-05-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="F97">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G97">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="H97">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>AP0089</v>
+        <v>AP0100</v>
       </c>
       <c r="B98" t="str">
-        <v>LDP-006</v>
+        <v>LDP-004</v>
       </c>
       <c r="C98" t="str">
-        <v>2026-05-13</v>
+        <v>2026-03-19</v>
       </c>
       <c r="D98" t="str">
         <v>Completed</v>
       </c>
       <c r="E98" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-24</v>
       </c>
       <c r="F98">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G98">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="H98">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>AP0090</v>
+        <v>AP0100</v>
       </c>
       <c r="B99" t="str">
-        <v>LDP-008</v>
+        <v>LDP-007</v>
       </c>
       <c r="C99" t="str">
-        <v>2026-03-07</v>
+        <v>2026-05-03</v>
       </c>
       <c r="D99" t="str">
         <v>Completed</v>
       </c>
       <c r="E99" t="str">
-        <v>2026-04-07</v>
+        <v>2026-05-21</v>
       </c>
       <c r="F99">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G99">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="H99">
         <v>4.3</v>
@@ -2975,247 +2975,247 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>AP0090</v>
+        <v>AP0101</v>
       </c>
       <c r="B100" t="str">
-        <v>LDP-009</v>
+        <v>LDP-008</v>
       </c>
       <c r="C100" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-16</v>
       </c>
       <c r="D100" t="str">
         <v>Completed</v>
       </c>
       <c r="E100" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-10</v>
       </c>
       <c r="F100">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G100">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H100">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>AP0090</v>
+        <v>AP0101</v>
       </c>
       <c r="B101" t="str">
-        <v>LDP-007</v>
+        <v>LDP-009</v>
       </c>
       <c r="C101" t="str">
-        <v>2026-05-08</v>
+        <v>2026-04-11</v>
       </c>
       <c r="D101" t="str">
-        <v>Enrolled</v>
+        <v>Completed</v>
       </c>
       <c r="E101" t="str">
-        <v/>
+        <v>2026-04-01</v>
       </c>
       <c r="F101">
-        <v>3</v>
-      </c>
-      <c r="G101" t="str">
-        <v/>
-      </c>
-      <c r="H101" t="str">
-        <v/>
+        <v>9</v>
+      </c>
+      <c r="G101">
+        <v>98</v>
+      </c>
+      <c r="H101">
+        <v>4.8</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>AP0091</v>
+        <v>AP0102</v>
       </c>
       <c r="B102" t="str">
-        <v>LDP-004</v>
+        <v>LDP-002</v>
       </c>
       <c r="C102" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-23</v>
       </c>
       <c r="D102" t="str">
         <v>Completed</v>
       </c>
       <c r="E102" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-25</v>
       </c>
       <c r="F102">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G102">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="H102">
-        <v>3.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>AP0092</v>
+        <v>AP0103</v>
       </c>
       <c r="B103" t="str">
-        <v>LDP-007</v>
+        <v>LDP-001</v>
       </c>
       <c r="C103" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-24</v>
       </c>
       <c r="D103" t="str">
-        <v>Completed</v>
+        <v>Dropped</v>
       </c>
       <c r="E103" t="str">
-        <v>2026-05-15</v>
+        <v/>
       </c>
       <c r="F103">
-        <v>5</v>
-      </c>
-      <c r="G103">
-        <v>87</v>
-      </c>
-      <c r="H103">
-        <v>4.6</v>
+        <v>3</v>
+      </c>
+      <c r="G103" t="str">
+        <v/>
+      </c>
+      <c r="H103" t="str">
+        <v/>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>AP0092</v>
+        <v>AP0103</v>
       </c>
       <c r="B104" t="str">
-        <v>LDP-002</v>
+        <v>LDP-010</v>
       </c>
       <c r="C104" t="str">
-        <v>2026-03-14</v>
+        <v>2026-03-22</v>
       </c>
       <c r="D104" t="str">
-        <v>Completed</v>
+        <v>Enrolled</v>
       </c>
       <c r="E104" t="str">
-        <v>2026-05-07</v>
+        <v/>
       </c>
       <c r="F104">
-        <v>16</v>
-      </c>
-      <c r="G104">
-        <v>59</v>
-      </c>
-      <c r="H104">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="G104" t="str">
+        <v/>
+      </c>
+      <c r="H104" t="str">
+        <v/>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>AP0092</v>
+        <v>AP0104</v>
       </c>
       <c r="B105" t="str">
-        <v>LDP-006</v>
+        <v>LDP-003</v>
       </c>
       <c r="C105" t="str">
-        <v>2026-04-17</v>
+        <v>2026-05-09</v>
       </c>
       <c r="D105" t="str">
-        <v>In-progress</v>
+        <v>Completed</v>
       </c>
       <c r="E105" t="str">
-        <v/>
+        <v>2026-05-06</v>
       </c>
       <c r="F105">
-        <v>6</v>
-      </c>
-      <c r="G105" t="str">
-        <v/>
-      </c>
-      <c r="H105" t="str">
-        <v/>
+        <v>8</v>
+      </c>
+      <c r="G105">
+        <v>88</v>
+      </c>
+      <c r="H105">
+        <v>4.4</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>AP0093</v>
+        <v>AP0105</v>
       </c>
       <c r="B106" t="str">
-        <v>LDP-009</v>
+        <v>LDP-003</v>
       </c>
       <c r="C106" t="str">
-        <v>2026-03-09</v>
+        <v>2026-04-08</v>
       </c>
       <c r="D106" t="str">
-        <v>Completed</v>
+        <v>Enrolled</v>
       </c>
       <c r="E106" t="str">
-        <v>2026-05-22</v>
+        <v/>
       </c>
       <c r="F106">
-        <v>5</v>
-      </c>
-      <c r="G106">
-        <v>57</v>
-      </c>
-      <c r="H106">
-        <v>3.9</v>
+        <v>10</v>
+      </c>
+      <c r="G106" t="str">
+        <v/>
+      </c>
+      <c r="H106" t="str">
+        <v/>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>AP0093</v>
+        <v>AP0105</v>
       </c>
       <c r="B107" t="str">
         <v>LDP-005</v>
       </c>
       <c r="C107" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-22</v>
       </c>
       <c r="D107" t="str">
         <v>Completed</v>
       </c>
       <c r="E107" t="str">
-        <v>2026-05-28</v>
+        <v>2026-04-27</v>
       </c>
       <c r="F107">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G107">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H107">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>AP0093</v>
+        <v>AP0106</v>
       </c>
       <c r="B108" t="str">
         <v>LDP-008</v>
       </c>
       <c r="C108" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-13</v>
       </c>
       <c r="D108" t="str">
         <v>Completed</v>
       </c>
       <c r="E108" t="str">
-        <v>2026-05-09</v>
+        <v>2026-04-08</v>
       </c>
       <c r="F108">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G108">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="H108">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>AP0096</v>
+        <v>AP0106</v>
       </c>
       <c r="B109" t="str">
         <v>LDP-001</v>
       </c>
       <c r="C109" t="str">
-        <v>2026-04-24</v>
+        <v>2026-03-17</v>
       </c>
       <c r="D109" t="str">
         <v>Dropped</v>
@@ -3224,7 +3224,7 @@
         <v/>
       </c>
       <c r="F109">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G109" t="str">
         <v/>
@@ -3235,143 +3235,143 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>AP0096</v>
+        <v>AP0107</v>
       </c>
       <c r="B110" t="str">
-        <v>LDP-010</v>
+        <v>LDP-006</v>
       </c>
       <c r="C110" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-20</v>
       </c>
       <c r="D110" t="str">
-        <v>Enrolled</v>
+        <v>Completed</v>
       </c>
       <c r="E110" t="str">
-        <v/>
+        <v>2026-05-21</v>
       </c>
       <c r="F110">
-        <v>3</v>
-      </c>
-      <c r="G110" t="str">
-        <v/>
-      </c>
-      <c r="H110" t="str">
-        <v/>
+        <v>14</v>
+      </c>
+      <c r="G110">
+        <v>81</v>
+      </c>
+      <c r="H110">
+        <v>4.6</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>AP0097</v>
+        <v>AP0108</v>
       </c>
       <c r="B111" t="str">
-        <v>LDP-003</v>
+        <v>LDP-002</v>
       </c>
       <c r="C111" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-13</v>
       </c>
       <c r="D111" t="str">
         <v>Completed</v>
       </c>
       <c r="E111" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-26</v>
       </c>
       <c r="F111">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G111">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="H111">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>AP0098</v>
+        <v>AP0108</v>
       </c>
       <c r="B112" t="str">
-        <v>LDP-003</v>
+        <v>LDP-005</v>
       </c>
       <c r="C112" t="str">
-        <v>2026-04-08</v>
+        <v>2026-03-04</v>
       </c>
       <c r="D112" t="str">
-        <v>Enrolled</v>
+        <v>Completed</v>
       </c>
       <c r="E112" t="str">
-        <v/>
+        <v>2026-04-28</v>
       </c>
       <c r="F112">
-        <v>10</v>
-      </c>
-      <c r="G112" t="str">
-        <v/>
-      </c>
-      <c r="H112" t="str">
-        <v/>
+        <v>9</v>
+      </c>
+      <c r="G112">
+        <v>97</v>
+      </c>
+      <c r="H112">
+        <v>3.3</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>AP0098</v>
+        <v>AP0108</v>
       </c>
       <c r="B113" t="str">
-        <v>LDP-005</v>
+        <v>LDP-007</v>
       </c>
       <c r="C113" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-13</v>
       </c>
       <c r="D113" t="str">
         <v>Completed</v>
       </c>
       <c r="E113" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-22</v>
       </c>
       <c r="F113">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G113">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="H113">
-        <v>4.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>AP0100</v>
+        <v>AP0109</v>
       </c>
       <c r="B114" t="str">
         <v>LDP-008</v>
       </c>
       <c r="C114" t="str">
-        <v>2026-03-13</v>
+        <v>2026-03-05</v>
       </c>
       <c r="D114" t="str">
         <v>Completed</v>
       </c>
       <c r="E114" t="str">
-        <v>2026-04-08</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F114">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G114">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="H114">
-        <v>4</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>AP0100</v>
+        <v>AP0109</v>
       </c>
       <c r="B115" t="str">
-        <v>LDP-001</v>
+        <v>LDP-009</v>
       </c>
       <c r="C115" t="str">
-        <v>2026-03-17</v>
+        <v>2026-04-16</v>
       </c>
       <c r="D115" t="str">
         <v>Dropped</v>
@@ -3380,7 +3380,7 @@
         <v/>
       </c>
       <c r="F115">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G115" t="str">
         <v/>
@@ -3391,129 +3391,129 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>AP0101</v>
+        <v>AP0110</v>
       </c>
       <c r="B116" t="str">
-        <v>LDP-006</v>
+        <v>LDP-004</v>
       </c>
       <c r="C116" t="str">
-        <v>2026-03-20</v>
+        <v>2026-05-02</v>
       </c>
       <c r="D116" t="str">
         <v>Completed</v>
       </c>
       <c r="E116" t="str">
-        <v>2026-05-21</v>
+        <v>2026-04-04</v>
       </c>
       <c r="F116">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G116">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="H116">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>AP0102</v>
+        <v>AP0110</v>
       </c>
       <c r="B117" t="str">
-        <v>LDP-002</v>
+        <v>LDP-009</v>
       </c>
       <c r="C117" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-01</v>
       </c>
       <c r="D117" t="str">
         <v>Completed</v>
       </c>
       <c r="E117" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-25</v>
       </c>
       <c r="F117">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="G117">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="H117">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>AP0102</v>
+        <v>AP0110</v>
       </c>
       <c r="B118" t="str">
-        <v>LDP-005</v>
+        <v>LDP-006</v>
       </c>
       <c r="C118" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-17</v>
       </c>
       <c r="D118" t="str">
         <v>Completed</v>
       </c>
       <c r="E118" t="str">
-        <v>2026-04-28</v>
+        <v>2026-04-08</v>
       </c>
       <c r="F118">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G118">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="H118">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>AP0102</v>
+        <v>AP0111</v>
       </c>
       <c r="B119" t="str">
-        <v>LDP-007</v>
+        <v>LDP-001</v>
       </c>
       <c r="C119" t="str">
-        <v>2026-03-13</v>
+        <v>2026-04-12</v>
       </c>
       <c r="D119" t="str">
         <v>Completed</v>
       </c>
       <c r="E119" t="str">
-        <v>2026-04-22</v>
+        <v>2026-05-20</v>
       </c>
       <c r="F119">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G119">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="H119">
-        <v>3</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>AP0103</v>
+        <v>AP0111</v>
       </c>
       <c r="B120" t="str">
-        <v>LDP-008</v>
+        <v>LDP-002</v>
       </c>
       <c r="C120" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-15</v>
       </c>
       <c r="D120" t="str">
         <v>Completed</v>
       </c>
       <c r="E120" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-17</v>
       </c>
       <c r="F120">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G120">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="H120">
         <v>4.7</v>
@@ -3521,441 +3521,441 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>AP0103</v>
+        <v>AP0111</v>
       </c>
       <c r="B121" t="str">
-        <v>LDP-009</v>
+        <v>LDP-007</v>
       </c>
       <c r="C121" t="str">
-        <v>2026-04-16</v>
+        <v>2026-03-16</v>
       </c>
       <c r="D121" t="str">
-        <v>Dropped</v>
+        <v>Completed</v>
       </c>
       <c r="E121" t="str">
-        <v/>
+        <v>2026-04-26</v>
       </c>
       <c r="F121">
-        <v>12</v>
-      </c>
-      <c r="G121" t="str">
-        <v/>
-      </c>
-      <c r="H121" t="str">
-        <v/>
+        <v>15</v>
+      </c>
+      <c r="G121">
+        <v>80</v>
+      </c>
+      <c r="H121">
+        <v>3.8</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>AP0104</v>
+        <v>AP0112</v>
       </c>
       <c r="B122" t="str">
-        <v>LDP-004</v>
+        <v>LDP-006</v>
       </c>
       <c r="C122" t="str">
-        <v>2026-05-02</v>
+        <v>2026-04-06</v>
       </c>
       <c r="D122" t="str">
         <v>Completed</v>
       </c>
       <c r="E122" t="str">
-        <v>2026-04-04</v>
+        <v>2026-05-06</v>
       </c>
       <c r="F122">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G122">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H122">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>AP0104</v>
+        <v>AP0115</v>
       </c>
       <c r="B123" t="str">
-        <v>LDP-009</v>
+        <v>LDP-002</v>
       </c>
       <c r="C123" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-05</v>
       </c>
       <c r="D123" t="str">
         <v>Completed</v>
       </c>
       <c r="E123" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F123">
         <v>2</v>
       </c>
       <c r="G123">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="H123">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>AP0104</v>
+        <v>AP0117</v>
       </c>
       <c r="B124" t="str">
-        <v>LDP-006</v>
+        <v>LDP-003</v>
       </c>
       <c r="C124" t="str">
-        <v>2026-03-17</v>
+        <v>2026-04-09</v>
       </c>
       <c r="D124" t="str">
         <v>Completed</v>
       </c>
       <c r="E124" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-14</v>
       </c>
       <c r="F124">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G124">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H124">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>AP0105</v>
+        <v>AP0117</v>
       </c>
       <c r="B125" t="str">
-        <v>LDP-001</v>
+        <v>LDP-004</v>
       </c>
       <c r="C125" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-20</v>
       </c>
       <c r="D125" t="str">
         <v>Completed</v>
       </c>
       <c r="E125" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-24</v>
       </c>
       <c r="F125">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G125">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="H125">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>AP0105</v>
+        <v>AP0117</v>
       </c>
       <c r="B126" t="str">
-        <v>LDP-002</v>
+        <v>LDP-007</v>
       </c>
       <c r="C126" t="str">
-        <v>2026-03-15</v>
+        <v>2026-04-06</v>
       </c>
       <c r="D126" t="str">
-        <v>Completed</v>
+        <v>Dropped</v>
       </c>
       <c r="E126" t="str">
-        <v>2026-05-17</v>
+        <v/>
       </c>
       <c r="F126">
-        <v>3</v>
-      </c>
-      <c r="G126">
-        <v>87</v>
-      </c>
-      <c r="H126">
-        <v>4.7</v>
+        <v>4</v>
+      </c>
+      <c r="G126" t="str">
+        <v/>
+      </c>
+      <c r="H126" t="str">
+        <v/>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>AP0105</v>
+        <v>AP0118</v>
       </c>
       <c r="B127" t="str">
-        <v>LDP-007</v>
+        <v>LDP-008</v>
       </c>
       <c r="C127" t="str">
-        <v>2026-03-16</v>
+        <v>2026-04-23</v>
       </c>
       <c r="D127" t="str">
         <v>Completed</v>
       </c>
       <c r="E127" t="str">
-        <v>2026-04-26</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F127">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G127">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="H127">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>AP0106</v>
+        <v>AP0118</v>
       </c>
       <c r="B128" t="str">
-        <v>LDP-006</v>
+        <v>LDP-004</v>
       </c>
       <c r="C128" t="str">
-        <v>2026-04-06</v>
+        <v>2026-05-24</v>
       </c>
       <c r="D128" t="str">
         <v>Completed</v>
       </c>
       <c r="E128" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="F128">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G128">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="H128">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>AP0109</v>
+        <v>AP0119</v>
       </c>
       <c r="B129" t="str">
-        <v>LDP-002</v>
+        <v>LDP-001</v>
       </c>
       <c r="C129" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-10</v>
       </c>
       <c r="D129" t="str">
         <v>Completed</v>
       </c>
       <c r="E129" t="str">
-        <v>2026-05-18</v>
+        <v>2026-04-03</v>
       </c>
       <c r="F129">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G129">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H129">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>AP0111</v>
+        <v>AP0120</v>
       </c>
       <c r="B130" t="str">
-        <v>LDP-003</v>
+        <v>LDP-001</v>
       </c>
       <c r="C130" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-08</v>
       </c>
       <c r="D130" t="str">
         <v>Completed</v>
       </c>
       <c r="E130" t="str">
-        <v>2026-04-14</v>
+        <v>2026-05-26</v>
       </c>
       <c r="F130">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="G130">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="H130">
-        <v>4.9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>AP0111</v>
+        <v>AP0121</v>
       </c>
       <c r="B131" t="str">
-        <v>LDP-004</v>
+        <v>LDP-006</v>
       </c>
       <c r="C131" t="str">
-        <v>2026-04-20</v>
+        <v>2026-03-04</v>
       </c>
       <c r="D131" t="str">
         <v>Completed</v>
       </c>
       <c r="E131" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-04</v>
       </c>
       <c r="F131">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G131">
         <v>72</v>
       </c>
       <c r="H131">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>AP0111</v>
+        <v>AP0123</v>
       </c>
       <c r="B132" t="str">
-        <v>LDP-007</v>
+        <v>LDP-003</v>
       </c>
       <c r="C132" t="str">
-        <v>2026-04-06</v>
+        <v>2026-05-11</v>
       </c>
       <c r="D132" t="str">
-        <v>Dropped</v>
+        <v>Completed</v>
       </c>
       <c r="E132" t="str">
-        <v/>
+        <v>2026-05-25</v>
       </c>
       <c r="F132">
-        <v>4</v>
-      </c>
-      <c r="G132" t="str">
-        <v/>
-      </c>
-      <c r="H132" t="str">
-        <v/>
+        <v>14</v>
+      </c>
+      <c r="G132">
+        <v>62</v>
+      </c>
+      <c r="H132">
+        <v>3.1</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>AP0112</v>
+        <v>AP0123</v>
       </c>
       <c r="B133" t="str">
-        <v>LDP-008</v>
+        <v>LDP-009</v>
       </c>
       <c r="C133" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-05</v>
       </c>
       <c r="D133" t="str">
         <v>Completed</v>
       </c>
       <c r="E133" t="str">
-        <v>2026-05-28</v>
+        <v>2026-04-05</v>
       </c>
       <c r="F133">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G133">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H133">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>AP0112</v>
+        <v>AP0123</v>
       </c>
       <c r="B134" t="str">
-        <v>LDP-004</v>
+        <v>LDP-005</v>
       </c>
       <c r="C134" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-08</v>
       </c>
       <c r="D134" t="str">
         <v>Completed</v>
       </c>
       <c r="E134" t="str">
-        <v>2026-05-07</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F134">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G134">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="H134">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>AP0113</v>
+        <v>AP0125</v>
       </c>
       <c r="B135" t="str">
-        <v>LDP-001</v>
+        <v>LDP-005</v>
       </c>
       <c r="C135" t="str">
-        <v>2026-05-10</v>
+        <v>2026-03-22</v>
       </c>
       <c r="D135" t="str">
-        <v>Completed</v>
+        <v>In-progress</v>
       </c>
       <c r="E135" t="str">
-        <v>2026-04-03</v>
+        <v/>
       </c>
       <c r="F135">
-        <v>9</v>
-      </c>
-      <c r="G135">
-        <v>74</v>
-      </c>
-      <c r="H135">
-        <v>3.3</v>
+        <v>4</v>
+      </c>
+      <c r="G135" t="str">
+        <v/>
+      </c>
+      <c r="H135" t="str">
+        <v/>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>AP0114</v>
+        <v>AP0128</v>
       </c>
       <c r="B136" t="str">
-        <v>LDP-001</v>
+        <v>LDP-008</v>
       </c>
       <c r="C136" t="str">
-        <v>2026-04-08</v>
+        <v>2026-05-10</v>
       </c>
       <c r="D136" t="str">
         <v>Completed</v>
       </c>
       <c r="E136" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-04</v>
       </c>
       <c r="F136">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G136">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="H136">
-        <v>5</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>AP0115</v>
+        <v>AP0128</v>
       </c>
       <c r="B137" t="str">
         <v>LDP-006</v>
       </c>
       <c r="C137" t="str">
-        <v>2026-03-04</v>
+        <v>2026-05-02</v>
       </c>
       <c r="D137" t="str">
         <v>Completed</v>
       </c>
       <c r="E137" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-19</v>
       </c>
       <c r="F137">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G137">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="H137">
         <v>4.1</v>
@@ -3963,77 +3963,77 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>AP0117</v>
+        <v>AP0128</v>
       </c>
       <c r="B138" t="str">
-        <v>LDP-003</v>
+        <v>LDP-004</v>
       </c>
       <c r="C138" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-02</v>
       </c>
       <c r="D138" t="str">
         <v>Completed</v>
       </c>
       <c r="E138" t="str">
-        <v>2026-05-25</v>
+        <v>2026-04-08</v>
       </c>
       <c r="F138">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G138">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="H138">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>AP0117</v>
+        <v>AP0129</v>
       </c>
       <c r="B139" t="str">
         <v>LDP-009</v>
       </c>
       <c r="C139" t="str">
-        <v>2026-04-05</v>
+        <v>2026-03-09</v>
       </c>
       <c r="D139" t="str">
-        <v>Completed</v>
+        <v>Dropped</v>
       </c>
       <c r="E139" t="str">
-        <v>2026-04-05</v>
+        <v/>
       </c>
       <c r="F139">
-        <v>2</v>
-      </c>
-      <c r="G139">
-        <v>65</v>
-      </c>
-      <c r="H139">
-        <v>4.4</v>
+        <v>3</v>
+      </c>
+      <c r="G139" t="str">
+        <v/>
+      </c>
+      <c r="H139" t="str">
+        <v/>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>AP0117</v>
+        <v>AP0130</v>
       </c>
       <c r="B140" t="str">
-        <v>LDP-005</v>
+        <v>LDP-007</v>
       </c>
       <c r="C140" t="str">
-        <v>2026-05-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="D140" t="str">
         <v>Completed</v>
       </c>
       <c r="E140" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-27</v>
       </c>
       <c r="F140">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G140">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="H140">
         <v>4.5</v>
@@ -4041,117 +4041,117 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>AP0119</v>
+        <v>AP0130</v>
       </c>
       <c r="B141" t="str">
-        <v>LDP-005</v>
+        <v>LDP-009</v>
       </c>
       <c r="C141" t="str">
-        <v>2026-03-22</v>
+        <v>2026-04-03</v>
       </c>
       <c r="D141" t="str">
-        <v>In-progress</v>
+        <v>Completed</v>
       </c>
       <c r="E141" t="str">
-        <v/>
+        <v>2026-05-08</v>
       </c>
       <c r="F141">
-        <v>4</v>
-      </c>
-      <c r="G141" t="str">
-        <v/>
-      </c>
-      <c r="H141" t="str">
-        <v/>
+        <v>7</v>
+      </c>
+      <c r="G141">
+        <v>62</v>
+      </c>
+      <c r="H141">
+        <v>3.7</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>AP0120</v>
+        <v>AP0130</v>
       </c>
       <c r="B142" t="str">
-        <v>LDP-008</v>
+        <v>LDP-003</v>
       </c>
       <c r="C142" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-21</v>
       </c>
       <c r="D142" t="str">
         <v>Completed</v>
       </c>
       <c r="E142" t="str">
-        <v>2026-05-04</v>
+        <v>2026-04-22</v>
       </c>
       <c r="F142">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G142">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="H142">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>AP0120</v>
+        <v>AP0132</v>
       </c>
       <c r="B143" t="str">
-        <v>LDP-006</v>
+        <v>LDP-008</v>
       </c>
       <c r="C143" t="str">
-        <v>2026-05-02</v>
+        <v>2026-04-12</v>
       </c>
       <c r="D143" t="str">
         <v>Completed</v>
       </c>
       <c r="E143" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-09</v>
       </c>
       <c r="F143">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G143">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="H143">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>AP0120</v>
+        <v>AP0135</v>
       </c>
       <c r="B144" t="str">
-        <v>LDP-004</v>
+        <v>LDP-002</v>
       </c>
       <c r="C144" t="str">
-        <v>2026-05-02</v>
+        <v>2026-03-16</v>
       </c>
       <c r="D144" t="str">
         <v>Completed</v>
       </c>
       <c r="E144" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-03</v>
       </c>
       <c r="F144">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G144">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H144">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>AP0121</v>
+        <v>AP0135</v>
       </c>
       <c r="B145" t="str">
-        <v>LDP-009</v>
+        <v>LDP-010</v>
       </c>
       <c r="C145" t="str">
-        <v>2026-03-09</v>
+        <v>2026-04-04</v>
       </c>
       <c r="D145" t="str">
         <v>Dropped</v>
@@ -4171,241 +4171,241 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>AP0122</v>
+        <v>AP0135</v>
       </c>
       <c r="B146" t="str">
-        <v>LDP-007</v>
+        <v>LDP-009</v>
       </c>
       <c r="C146" t="str">
-        <v>2026-03-09</v>
+        <v>2026-05-16</v>
       </c>
       <c r="D146" t="str">
-        <v>Completed</v>
+        <v>In-progress</v>
       </c>
       <c r="E146" t="str">
-        <v>2026-05-27</v>
+        <v/>
       </c>
       <c r="F146">
-        <v>6</v>
-      </c>
-      <c r="G146">
-        <v>88</v>
-      </c>
-      <c r="H146">
-        <v>4.5</v>
+        <v>9</v>
+      </c>
+      <c r="G146" t="str">
+        <v/>
+      </c>
+      <c r="H146" t="str">
+        <v/>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>AP0122</v>
+        <v>AP0136</v>
       </c>
       <c r="B147" t="str">
-        <v>LDP-009</v>
+        <v>LDP-005</v>
       </c>
       <c r="C147" t="str">
-        <v>2026-04-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="D147" t="str">
         <v>Completed</v>
       </c>
       <c r="E147" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="F147">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G147">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="H147">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>AP0122</v>
+        <v>AP0136</v>
       </c>
       <c r="B148" t="str">
-        <v>LDP-003</v>
+        <v>LDP-007</v>
       </c>
       <c r="C148" t="str">
-        <v>2026-05-21</v>
+        <v>2026-04-14</v>
       </c>
       <c r="D148" t="str">
         <v>Completed</v>
       </c>
       <c r="E148" t="str">
-        <v>2026-04-22</v>
+        <v>2026-05-03</v>
       </c>
       <c r="F148">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G148">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H148">
-        <v>3.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>AP0124</v>
+        <v>AP0137</v>
       </c>
       <c r="B149" t="str">
-        <v>LDP-008</v>
+        <v>LDP-001</v>
       </c>
       <c r="C149" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-01</v>
       </c>
       <c r="D149" t="str">
         <v>Completed</v>
       </c>
       <c r="E149" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-08</v>
       </c>
       <c r="F149">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G149">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="H149">
-        <v>3.9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>AP0128</v>
+        <v>AP0137</v>
       </c>
       <c r="B150" t="str">
-        <v>LDP-002</v>
+        <v>LDP-006</v>
       </c>
       <c r="C150" t="str">
-        <v>2026-03-16</v>
+        <v>2026-05-25</v>
       </c>
       <c r="D150" t="str">
         <v>Completed</v>
       </c>
       <c r="E150" t="str">
-        <v>2026-04-03</v>
+        <v>2026-04-10</v>
       </c>
       <c r="F150">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G150">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="H150">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>AP0128</v>
+        <v>AP0138</v>
       </c>
       <c r="B151" t="str">
-        <v>LDP-010</v>
+        <v>LDP-003</v>
       </c>
       <c r="C151" t="str">
-        <v>2026-04-04</v>
+        <v>2026-05-09</v>
       </c>
       <c r="D151" t="str">
-        <v>Dropped</v>
+        <v>Completed</v>
       </c>
       <c r="E151" t="str">
-        <v/>
+        <v>2026-04-27</v>
       </c>
       <c r="F151">
-        <v>3</v>
-      </c>
-      <c r="G151" t="str">
-        <v/>
-      </c>
-      <c r="H151" t="str">
-        <v/>
+        <v>8</v>
+      </c>
+      <c r="G151">
+        <v>67</v>
+      </c>
+      <c r="H151">
+        <v>4.1</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>AP0128</v>
+        <v>AP0139</v>
       </c>
       <c r="B152" t="str">
-        <v>LDP-009</v>
+        <v>LDP-008</v>
       </c>
       <c r="C152" t="str">
-        <v>2026-05-16</v>
+        <v>2026-03-20</v>
       </c>
       <c r="D152" t="str">
-        <v>In-progress</v>
+        <v>Completed</v>
       </c>
       <c r="E152" t="str">
-        <v/>
+        <v>2026-05-02</v>
       </c>
       <c r="F152">
-        <v>9</v>
-      </c>
-      <c r="G152" t="str">
-        <v/>
-      </c>
-      <c r="H152" t="str">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="G152">
+        <v>85</v>
+      </c>
+      <c r="H152">
+        <v>3.3</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>AP0129</v>
+        <v>AP0140</v>
       </c>
       <c r="B153" t="str">
-        <v>LDP-005</v>
+        <v>LDP-001</v>
       </c>
       <c r="C153" t="str">
-        <v>2026-03-04</v>
+        <v>2026-04-11</v>
       </c>
       <c r="D153" t="str">
         <v>Completed</v>
       </c>
       <c r="E153" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F153">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G153">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="H153">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>AP0129</v>
+        <v>AP0141</v>
       </c>
       <c r="B154" t="str">
         <v>LDP-007</v>
       </c>
       <c r="C154" t="str">
-        <v>2026-04-14</v>
+        <v>2026-03-07</v>
       </c>
       <c r="D154" t="str">
-        <v>Completed</v>
+        <v>In-progress</v>
       </c>
       <c r="E154" t="str">
-        <v>2026-05-03</v>
+        <v/>
       </c>
       <c r="F154">
-        <v>15</v>
-      </c>
-      <c r="G154">
-        <v>72</v>
-      </c>
-      <c r="H154">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G154" t="str">
+        <v/>
+      </c>
+      <c r="H154" t="str">
+        <v/>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>AP0130</v>
+        <v>AP0141</v>
       </c>
       <c r="B155" t="str">
         <v>LDP-001</v>
@@ -4417,79 +4417,79 @@
         <v>Completed</v>
       </c>
       <c r="E155" t="str">
-        <v>2026-05-08</v>
+        <v>2026-04-28</v>
       </c>
       <c r="F155">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G155">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="H155">
-        <v>4</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>AP0130</v>
+        <v>AP0142</v>
       </c>
       <c r="B156" t="str">
-        <v>LDP-006</v>
+        <v>LDP-001</v>
       </c>
       <c r="C156" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-03</v>
       </c>
       <c r="D156" t="str">
         <v>Completed</v>
       </c>
       <c r="E156" t="str">
-        <v>2026-04-10</v>
+        <v>2026-05-04</v>
       </c>
       <c r="F156">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G156">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="H156">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>AP0131</v>
+        <v>AP0142</v>
       </c>
       <c r="B157" t="str">
-        <v>LDP-003</v>
+        <v>LDP-006</v>
       </c>
       <c r="C157" t="str">
-        <v>2026-05-09</v>
+        <v>2026-03-17</v>
       </c>
       <c r="D157" t="str">
         <v>Completed</v>
       </c>
       <c r="E157" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-10</v>
       </c>
       <c r="F157">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G157">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H157">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>AP0132</v>
+        <v>AP0144</v>
       </c>
       <c r="B158" t="str">
-        <v>LDP-008</v>
+        <v>LDP-006</v>
       </c>
       <c r="C158" t="str">
-        <v>2026-03-20</v>
+        <v>2026-05-09</v>
       </c>
       <c r="D158" t="str">
         <v>Completed</v>
@@ -4498,59 +4498,59 @@
         <v>2026-05-02</v>
       </c>
       <c r="F158">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G158">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="H158">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>AP0134</v>
+        <v>AP0144</v>
       </c>
       <c r="B159" t="str">
-        <v>LDP-001</v>
+        <v>LDP-005</v>
       </c>
       <c r="C159" t="str">
-        <v>2026-04-11</v>
+        <v>2026-05-05</v>
       </c>
       <c r="D159" t="str">
         <v>Completed</v>
       </c>
       <c r="E159" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-13</v>
       </c>
       <c r="F159">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G159">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="H159">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>AP0135</v>
+        <v>AP0144</v>
       </c>
       <c r="B160" t="str">
-        <v>LDP-007</v>
+        <v>LDP-001</v>
       </c>
       <c r="C160" t="str">
-        <v>2026-03-07</v>
+        <v>2026-04-15</v>
       </c>
       <c r="D160" t="str">
-        <v>In-progress</v>
+        <v>Enrolled</v>
       </c>
       <c r="E160" t="str">
         <v/>
       </c>
       <c r="F160">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G160" t="str">
         <v/>
@@ -4561,657 +4561,241 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>AP0135</v>
+        <v>AP0145</v>
       </c>
       <c r="B161" t="str">
-        <v>LDP-001</v>
+        <v>LDP-010</v>
       </c>
       <c r="C161" t="str">
-        <v>2026-04-01</v>
+        <v>2026-03-19</v>
       </c>
       <c r="D161" t="str">
         <v>Completed</v>
       </c>
       <c r="E161" t="str">
-        <v>2026-04-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="F161">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G161">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="H161">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>AP0136</v>
+        <v>AP0145</v>
       </c>
       <c r="B162" t="str">
-        <v>LDP-001</v>
+        <v>LDP-007</v>
       </c>
       <c r="C162" t="str">
-        <v>2026-05-03</v>
+        <v>2026-03-10</v>
       </c>
       <c r="D162" t="str">
-        <v>Completed</v>
+        <v>In-progress</v>
       </c>
       <c r="E162" t="str">
-        <v>2026-05-04</v>
+        <v/>
       </c>
       <c r="F162">
-        <v>4</v>
-      </c>
-      <c r="G162">
-        <v>57</v>
-      </c>
-      <c r="H162">
-        <v>4.3</v>
+        <v>15</v>
+      </c>
+      <c r="G162" t="str">
+        <v/>
+      </c>
+      <c r="H162" t="str">
+        <v/>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>AP0136</v>
+        <v>AP0145</v>
       </c>
       <c r="B163" t="str">
-        <v>LDP-006</v>
+        <v>LDP-008</v>
       </c>
       <c r="C163" t="str">
-        <v>2026-03-17</v>
+        <v>2026-04-12</v>
       </c>
       <c r="D163" t="str">
         <v>Completed</v>
       </c>
       <c r="E163" t="str">
-        <v>2026-04-10</v>
+        <v>2026-05-13</v>
       </c>
       <c r="F163">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G163">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="H163">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>AP0138</v>
+        <v>AP0146</v>
       </c>
       <c r="B164" t="str">
-        <v>LDP-006</v>
+        <v>LDP-004</v>
       </c>
       <c r="C164" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-16</v>
       </c>
       <c r="D164" t="str">
         <v>Completed</v>
       </c>
       <c r="E164" t="str">
-        <v>2026-05-02</v>
+        <v>2026-05-17</v>
       </c>
       <c r="F164">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G164">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="H164">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>AP0138</v>
+        <v>AP0146</v>
       </c>
       <c r="B165" t="str">
-        <v>LDP-005</v>
+        <v>LDP-010</v>
       </c>
       <c r="C165" t="str">
-        <v>2026-05-05</v>
+        <v>2026-04-15</v>
       </c>
       <c r="D165" t="str">
         <v>Completed</v>
       </c>
       <c r="E165" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="F165">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G165">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="H165">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>AP0138</v>
+        <v>AP0146</v>
       </c>
       <c r="B166" t="str">
-        <v>LDP-001</v>
+        <v>LDP-003</v>
       </c>
       <c r="C166" t="str">
-        <v>2026-04-15</v>
+        <v>2026-03-22</v>
       </c>
       <c r="D166" t="str">
-        <v>Enrolled</v>
+        <v>Completed</v>
       </c>
       <c r="E166" t="str">
-        <v/>
+        <v>2026-05-09</v>
       </c>
       <c r="F166">
-        <v>3</v>
-      </c>
-      <c r="G166" t="str">
-        <v/>
-      </c>
-      <c r="H166" t="str">
-        <v/>
+        <v>5</v>
+      </c>
+      <c r="G166">
+        <v>77</v>
+      </c>
+      <c r="H166">
+        <v>4.1</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>AP0139</v>
+        <v>AP0147</v>
       </c>
       <c r="B167" t="str">
-        <v>LDP-010</v>
+        <v>LDP-006</v>
       </c>
       <c r="C167" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-09</v>
       </c>
       <c r="D167" t="str">
-        <v>Completed</v>
+        <v>In-progress</v>
       </c>
       <c r="E167" t="str">
-        <v>2026-05-23</v>
+        <v/>
       </c>
       <c r="F167">
-        <v>5</v>
-      </c>
-      <c r="G167">
-        <v>69</v>
-      </c>
-      <c r="H167">
-        <v>3.6</v>
+        <v>6</v>
+      </c>
+      <c r="G167" t="str">
+        <v/>
+      </c>
+      <c r="H167" t="str">
+        <v/>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>AP0139</v>
+        <v>AP0147</v>
       </c>
       <c r="B168" t="str">
-        <v>LDP-007</v>
+        <v>LDP-009</v>
       </c>
       <c r="C168" t="str">
-        <v>2026-03-10</v>
+        <v>2026-05-02</v>
       </c>
       <c r="D168" t="str">
-        <v>In-progress</v>
+        <v>Completed</v>
       </c>
       <c r="E168" t="str">
-        <v/>
+        <v>2026-04-16</v>
       </c>
       <c r="F168">
         <v>15</v>
       </c>
-      <c r="G168" t="str">
-        <v/>
-      </c>
-      <c r="H168" t="str">
-        <v/>
+      <c r="G168">
+        <v>82</v>
+      </c>
+      <c r="H168">
+        <v>3.6</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>AP0139</v>
+        <v>AP0148</v>
       </c>
       <c r="B169" t="str">
-        <v>LDP-008</v>
+        <v>LDP-005</v>
       </c>
       <c r="C169" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-01</v>
       </c>
       <c r="D169" t="str">
         <v>Completed</v>
       </c>
       <c r="E169" t="str">
-        <v>2026-05-13</v>
+        <v>2026-04-10</v>
       </c>
       <c r="F169">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G169">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="H169">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="str">
-        <v>AP0140</v>
-      </c>
-      <c r="B170" t="str">
-        <v>LDP-004</v>
-      </c>
-      <c r="C170" t="str">
-        <v>2026-05-16</v>
-      </c>
-      <c r="D170" t="str">
-        <v>Completed</v>
-      </c>
-      <c r="E170" t="str">
-        <v>2026-05-17</v>
-      </c>
-      <c r="F170">
-        <v>12</v>
-      </c>
-      <c r="G170">
-        <v>55</v>
-      </c>
-      <c r="H170">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="str">
-        <v>AP0140</v>
-      </c>
-      <c r="B171" t="str">
-        <v>LDP-010</v>
-      </c>
-      <c r="C171" t="str">
-        <v>2026-04-15</v>
-      </c>
-      <c r="D171" t="str">
-        <v>Completed</v>
-      </c>
-      <c r="E171" t="str">
-        <v>2026-05-16</v>
-      </c>
-      <c r="F171">
-        <v>16</v>
-      </c>
-      <c r="G171">
-        <v>59</v>
-      </c>
-      <c r="H171">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="str">
-        <v>AP0140</v>
-      </c>
-      <c r="B172" t="str">
-        <v>LDP-003</v>
-      </c>
-      <c r="C172" t="str">
-        <v>2026-03-22</v>
-      </c>
-      <c r="D172" t="str">
-        <v>Completed</v>
-      </c>
-      <c r="E172" t="str">
-        <v>2026-05-09</v>
-      </c>
-      <c r="F172">
-        <v>5</v>
-      </c>
-      <c r="G172">
-        <v>77</v>
-      </c>
-      <c r="H172">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="str">
-        <v>AP0141</v>
-      </c>
-      <c r="B173" t="str">
-        <v>LDP-006</v>
-      </c>
-      <c r="C173" t="str">
-        <v>2026-03-09</v>
-      </c>
-      <c r="D173" t="str">
-        <v>In-progress</v>
-      </c>
-      <c r="E173" t="str">
-        <v/>
-      </c>
-      <c r="F173">
-        <v>6</v>
-      </c>
-      <c r="G173" t="str">
-        <v/>
-      </c>
-      <c r="H173" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="str">
-        <v>AP0141</v>
-      </c>
-      <c r="B174" t="str">
-        <v>LDP-009</v>
-      </c>
-      <c r="C174" t="str">
-        <v>2026-05-02</v>
-      </c>
-      <c r="D174" t="str">
-        <v>Completed</v>
-      </c>
-      <c r="E174" t="str">
-        <v>2026-04-16</v>
-      </c>
-      <c r="F174">
-        <v>15</v>
-      </c>
-      <c r="G174">
-        <v>82</v>
-      </c>
-      <c r="H174">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="str">
-        <v>AP0142</v>
-      </c>
-      <c r="B175" t="str">
-        <v>LDP-005</v>
-      </c>
-      <c r="C175" t="str">
-        <v>2026-04-01</v>
-      </c>
-      <c r="D175" t="str">
-        <v>Completed</v>
-      </c>
-      <c r="E175" t="str">
-        <v>2026-04-10</v>
-      </c>
-      <c r="F175">
-        <v>3</v>
-      </c>
-      <c r="G175">
-        <v>63</v>
-      </c>
-      <c r="H175">
         <v>4.5</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="str">
-        <v>AP0143</v>
-      </c>
-      <c r="B176" t="str">
-        <v>LDP-009</v>
-      </c>
-      <c r="C176" t="str">
-        <v>2026-03-21</v>
-      </c>
-      <c r="D176" t="str">
-        <v>Completed</v>
-      </c>
-      <c r="E176" t="str">
-        <v>2026-04-07</v>
-      </c>
-      <c r="F176">
-        <v>10</v>
-      </c>
-      <c r="G176">
-        <v>64</v>
-      </c>
-      <c r="H176">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="str">
-        <v>AP0143</v>
-      </c>
-      <c r="B177" t="str">
-        <v>LDP-001</v>
-      </c>
-      <c r="C177" t="str">
-        <v>2026-03-21</v>
-      </c>
-      <c r="D177" t="str">
-        <v>Completed</v>
-      </c>
-      <c r="E177" t="str">
-        <v>2026-04-13</v>
-      </c>
-      <c r="F177">
-        <v>11</v>
-      </c>
-      <c r="G177">
-        <v>66</v>
-      </c>
-      <c r="H177">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="str">
-        <v>AP0144</v>
-      </c>
-      <c r="B178" t="str">
-        <v>LDP-009</v>
-      </c>
-      <c r="C178" t="str">
-        <v>2026-05-14</v>
-      </c>
-      <c r="D178" t="str">
-        <v>Completed</v>
-      </c>
-      <c r="E178" t="str">
-        <v>2026-04-14</v>
-      </c>
-      <c r="F178">
-        <v>4</v>
-      </c>
-      <c r="G178">
-        <v>98</v>
-      </c>
-      <c r="H178">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="str">
-        <v>AP0144</v>
-      </c>
-      <c r="B179" t="str">
-        <v>LDP-006</v>
-      </c>
-      <c r="C179" t="str">
-        <v>2026-04-04</v>
-      </c>
-      <c r="D179" t="str">
-        <v>Completed</v>
-      </c>
-      <c r="E179" t="str">
-        <v>2026-05-27</v>
-      </c>
-      <c r="F179">
-        <v>15</v>
-      </c>
-      <c r="G179">
-        <v>93</v>
-      </c>
-      <c r="H179">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="str">
-        <v>AP0144</v>
-      </c>
-      <c r="B180" t="str">
-        <v>LDP-008</v>
-      </c>
-      <c r="C180" t="str">
-        <v>2026-04-07</v>
-      </c>
-      <c r="D180" t="str">
-        <v>Completed</v>
-      </c>
-      <c r="E180" t="str">
-        <v>2026-04-27</v>
-      </c>
-      <c r="F180">
-        <v>4</v>
-      </c>
-      <c r="G180">
-        <v>75</v>
-      </c>
-      <c r="H180">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="str">
-        <v>AP0147</v>
-      </c>
-      <c r="B181" t="str">
-        <v>LDP-009</v>
-      </c>
-      <c r="C181" t="str">
-        <v>2026-05-22</v>
-      </c>
-      <c r="D181" t="str">
-        <v>In-progress</v>
-      </c>
-      <c r="E181" t="str">
-        <v/>
-      </c>
-      <c r="F181">
-        <v>6</v>
-      </c>
-      <c r="G181" t="str">
-        <v/>
-      </c>
-      <c r="H181" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="str">
-        <v>AP0147</v>
-      </c>
-      <c r="B182" t="str">
-        <v>LDP-004</v>
-      </c>
-      <c r="C182" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="D182" t="str">
-        <v>Completed</v>
-      </c>
-      <c r="E182" t="str">
-        <v>2026-04-20</v>
-      </c>
-      <c r="F182">
-        <v>3</v>
-      </c>
-      <c r="G182">
-        <v>95</v>
-      </c>
-      <c r="H182">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="str">
-        <v>AP0148</v>
-      </c>
-      <c r="B183" t="str">
-        <v>LDP-010</v>
-      </c>
-      <c r="C183" t="str">
-        <v>2026-03-05</v>
-      </c>
-      <c r="D183" t="str">
-        <v>Completed</v>
-      </c>
-      <c r="E183" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="F183">
-        <v>6</v>
-      </c>
-      <c r="G183">
-        <v>67</v>
-      </c>
-      <c r="H183">
-        <v>4.9</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="str">
-        <v>AP0148</v>
-      </c>
-      <c r="B184" t="str">
-        <v>LDP-006</v>
-      </c>
-      <c r="C184" t="str">
-        <v>2026-05-16</v>
-      </c>
-      <c r="D184" t="str">
-        <v>Dropped</v>
-      </c>
-      <c r="E184" t="str">
-        <v/>
-      </c>
-      <c r="F184">
-        <v>15</v>
-      </c>
-      <c r="G184" t="str">
-        <v/>
-      </c>
-      <c r="H184" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="str">
-        <v>AP0148</v>
-      </c>
-      <c r="B185" t="str">
-        <v>LDP-003</v>
-      </c>
-      <c r="C185" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="D185" t="str">
-        <v>Completed</v>
-      </c>
-      <c r="E185" t="str">
-        <v>2026-05-02</v>
-      </c>
-      <c r="F185">
-        <v>5</v>
-      </c>
-      <c r="G185">
-        <v>86</v>
-      </c>
-      <c r="H185">
-        <v>4.4</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H185"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H169"/>
   </ignoredErrors>
 </worksheet>
 </file>